--- a/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>FKWL</t>
   </si>
@@ -656,429 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E8" s="3">
         <v>9700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>44300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>66200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>62600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>14600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>36800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>55000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>50900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>11200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>11500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>10400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1600</v>
       </c>
       <c r="I10" s="3">
         <v>1600</v>
       </c>
       <c r="J10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K10" s="3">
         <v>1400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1500</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>1400</v>
       </c>
       <c r="AB10" s="3">
         <v>1400</v>
       </c>
       <c r="AC10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD10" s="3">
         <v>2200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2900</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>2300</v>
       </c>
       <c r="AG10" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1124,16 +1137,16 @@
         <v>900</v>
       </c>
       <c r="F12" s="3">
+        <v>900</v>
+      </c>
+      <c r="G12" s="3">
         <v>1100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1000</v>
       </c>
       <c r="H12" s="3">
         <v>1000</v>
       </c>
       <c r="I12" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="J12" s="3">
         <v>1100</v>
@@ -1142,10 +1155,10 @@
         <v>1100</v>
       </c>
       <c r="L12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M12" s="3">
         <v>1000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1200</v>
       </c>
       <c r="N12" s="3">
         <v>1200</v>
@@ -1154,40 +1167,40 @@
         <v>1200</v>
       </c>
       <c r="P12" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="Q12" s="3">
         <v>1000</v>
       </c>
       <c r="R12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S12" s="3">
         <v>800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>800</v>
-      </c>
-      <c r="V12" s="3">
-        <v>700</v>
       </c>
       <c r="W12" s="3">
         <v>700</v>
       </c>
       <c r="X12" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y12" s="3">
         <v>800</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>700</v>
       </c>
       <c r="Z12" s="3">
         <v>700</v>
       </c>
       <c r="AA12" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB12" s="3">
         <v>900</v>
@@ -1202,13 +1215,16 @@
         <v>900</v>
       </c>
       <c r="AF12" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AG12" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1302,49 +1318,52 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2400</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-500</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>91</v>
@@ -1361,8 +1380,8 @@
       <c r="U14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1397,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1492,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>91</v>
+      <c r="D17" s="3">
+        <v>10400</v>
       </c>
       <c r="E17" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F17" s="3">
         <v>19300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>57000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>53400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>91</v>
+      <c r="D18" s="3">
+        <v>-1600</v>
       </c>
       <c r="E18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5200</v>
-      </c>
-      <c r="O18" s="3">
-        <v>9200</v>
       </c>
       <c r="P18" s="3">
         <v>9200</v>
       </c>
       <c r="Q18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="R18" s="3">
         <v>4800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-700</v>
       </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
       <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>700</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>400</v>
       </c>
       <c r="AG18" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1749,59 +1781,60 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>91</v>
+      <c r="D20" s="3">
+        <v>700</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1815,19 +1848,19 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>100</v>
       </c>
       <c r="AC20" s="3">
         <v>100</v>
@@ -1839,108 +1872,114 @@
         <v>100</v>
       </c>
       <c r="AF20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>91</v>
+      <c r="D21" s="3">
+        <v>-600</v>
       </c>
       <c r="E21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5500</v>
-      </c>
-      <c r="O21" s="3">
-        <v>9300</v>
       </c>
       <c r="P21" s="3">
         <v>9300</v>
       </c>
       <c r="Q21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="R21" s="3">
         <v>5000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-400</v>
       </c>
       <c r="AB21" s="3">
         <v>-400</v>
       </c>
       <c r="AC21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD21" s="3">
         <v>200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2034,198 +2073,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>100</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
         <v>800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
       </c>
       <c r="U24" s="3">
+        <v>100</v>
+      </c>
+      <c r="V24" s="3">
         <v>-300</v>
-      </c>
-      <c r="V24" s="3">
-        <v>-100</v>
       </c>
       <c r="W24" s="3">
         <v>-100</v>
       </c>
       <c r="X24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-100</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2319,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>91</v>
+      <c r="D26" s="3">
+        <v>-600</v>
       </c>
       <c r="E26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1100</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>4200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AC26" s="3">
-        <v>0</v>
-      </c>
       <c r="AD26" s="3">
         <v>0</v>
       </c>
       <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3">
         <v>500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>91</v>
+      <c r="D27" s="3">
+        <v>-800</v>
       </c>
       <c r="E27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>3900</v>
-      </c>
-      <c r="O27" s="3">
-        <v>6900</v>
       </c>
       <c r="P27" s="3">
         <v>6900</v>
       </c>
       <c r="Q27" s="3">
+        <v>6900</v>
+      </c>
+      <c r="R27" s="3">
         <v>3700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>200</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-100</v>
       </c>
       <c r="Z27" s="3">
         <v>-100</v>
       </c>
       <c r="AA27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
-        <v>0</v>
-      </c>
       <c r="AD27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="3">
         <v>100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2639,8 +2699,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>91</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>91</v>
@@ -2660,11 +2720,11 @@
       <c r="T29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="V29" s="3">
         <v>-100</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>91</v>
@@ -2672,11 +2732,11 @@
       <c r="X29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-700</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>91</v>
@@ -2687,8 +2747,8 @@
       <c r="AC29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
@@ -2699,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2889,59 +2955,62 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>91</v>
+      <c r="D32" s="3">
+        <v>-700</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2955,19 +3024,19 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-100</v>
       </c>
       <c r="AC32" s="3">
         <v>-100</v>
@@ -2979,108 +3048,114 @@
         <v>-100</v>
       </c>
       <c r="AF32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>91</v>
+      <c r="D33" s="3">
+        <v>-800</v>
       </c>
       <c r="E33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>3900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>6900</v>
       </c>
       <c r="P33" s="3">
         <v>6900</v>
       </c>
       <c r="Q33" s="3">
+        <v>6900</v>
+      </c>
+      <c r="R33" s="3">
         <v>3700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AC33" s="3">
-        <v>0</v>
-      </c>
       <c r="AD33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="3">
         <v>100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3174,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>91</v>
+      <c r="D35" s="3">
+        <v>-800</v>
       </c>
       <c r="E35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>3900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>6900</v>
       </c>
       <c r="P35" s="3">
         <v>6900</v>
       </c>
       <c r="Q35" s="3">
+        <v>6900</v>
+      </c>
+      <c r="R35" s="3">
         <v>3700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AC35" s="3">
-        <v>0</v>
-      </c>
       <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="3">
         <v>100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3439,129 +3524,133 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>39300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>45800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>54400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>71000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>28200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>14300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E42" s="3">
         <v>26800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>16600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>16300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6600</v>
-      </c>
-      <c r="K42" s="3">
-        <v>5400</v>
       </c>
       <c r="L42" s="3">
         <v>5400</v>
@@ -3593,8 +3682,8 @@
       <c r="U42" s="3">
         <v>5400</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>91</v>
+      <c r="V42" s="3">
+        <v>5400</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>91</v>
@@ -3608,8 +3697,8 @@
       <c r="Z42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3629,203 +3718,212 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E43" s="3">
         <v>10000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>27900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>11100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>9600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>13800</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>12400</v>
       </c>
       <c r="AG43" s="3">
         <v>12400</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>12400</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E44" s="3">
         <v>2300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>11800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>800</v>
-      </c>
-      <c r="W44" s="3">
-        <v>1900</v>
       </c>
       <c r="X44" s="3">
         <v>1900</v>
       </c>
       <c r="Y44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z44" s="3">
         <v>1600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -3834,25 +3932,25 @@
         <v>100</v>
       </c>
       <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
         <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
       </c>
       <c r="I45" s="3">
         <v>200</v>
       </c>
       <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
@@ -3864,7 +3962,7 @@
         <v>100</v>
       </c>
       <c r="Q45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -3876,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
@@ -3891,19 +3989,19 @@
         <v>100</v>
       </c>
       <c r="Z45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>200</v>
       </c>
       <c r="AB45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC45" s="3">
         <v>100</v>
       </c>
       <c r="AD45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AE45" s="3">
         <v>500</v>
@@ -3912,105 +4010,111 @@
         <v>500</v>
       </c>
       <c r="AG45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E46" s="3">
         <v>46100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>51900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>47300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>50400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>47000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>48400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>53300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>45500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>47200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>54800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>74400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>106100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>79400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>61400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>25100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>20700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>19600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>21600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>27600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>21700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>21900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>21200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>28900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>23900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>28100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>25900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>27900</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -4104,64 +4208,67 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>100</v>
+      </c>
+      <c r="E48" s="3">
         <v>200</v>
-      </c>
-      <c r="E48" s="3">
-        <v>300</v>
       </c>
       <c r="F48" s="3">
         <v>300</v>
       </c>
       <c r="G48" s="3">
+        <v>300</v>
+      </c>
+      <c r="H48" s="3">
         <v>400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>600</v>
       </c>
       <c r="J48" s="3">
         <v>600</v>
       </c>
       <c r="K48" s="3">
+        <v>600</v>
+      </c>
+      <c r="L48" s="3">
         <v>700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1500</v>
-      </c>
-      <c r="S48" s="3">
-        <v>1600</v>
       </c>
       <c r="T48" s="3">
         <v>1600</v>
       </c>
       <c r="U48" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="V48" s="3">
         <v>100</v>
@@ -4179,7 +4286,7 @@
         <v>100</v>
       </c>
       <c r="AA48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB48" s="3">
         <v>200</v>
@@ -4191,7 +4298,7 @@
         <v>200</v>
       </c>
       <c r="AE48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF48" s="3">
         <v>300</v>
@@ -4199,103 +4306,109 @@
       <c r="AG48" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1600</v>
       </c>
       <c r="J49" s="3">
         <v>1600</v>
       </c>
       <c r="K49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L49" s="3">
         <v>1700</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1500</v>
       </c>
       <c r="M49" s="3">
         <v>1500</v>
       </c>
       <c r="N49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O49" s="3">
         <v>1600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1700</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1400</v>
       </c>
       <c r="Q49" s="3">
         <v>1400</v>
       </c>
       <c r="R49" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="S49" s="3">
         <v>1500</v>
       </c>
       <c r="T49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U49" s="3">
         <v>1700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1400</v>
-      </c>
-      <c r="V49" s="3">
-        <v>1100</v>
       </c>
       <c r="W49" s="3">
         <v>1100</v>
       </c>
       <c r="X49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y49" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>1300</v>
       </c>
       <c r="Z49" s="3">
         <v>1300</v>
       </c>
       <c r="AA49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB49" s="3">
         <v>1400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>1300</v>
       </c>
       <c r="AE49" s="3">
         <v>1300</v>
       </c>
       <c r="AF49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="AG49" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4484,91 +4600,94 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="E52" s="3">
         <v>2400</v>
       </c>
       <c r="F52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G52" s="3">
         <v>2000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2100</v>
-      </c>
-      <c r="X52" s="3">
-        <v>2000</v>
       </c>
       <c r="Y52" s="3">
         <v>2000</v>
       </c>
       <c r="Z52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1800</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>1900</v>
       </c>
       <c r="AE52" s="3">
         <v>1900</v>
@@ -4577,10 +4696,13 @@
         <v>1900</v>
       </c>
       <c r="AG52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AH52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4674,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E54" s="3">
         <v>50900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>56900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>52400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>54600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>51000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>52000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>57200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>49400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>50500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>78000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>109700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>83100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>65400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>30300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>30800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>24900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>30800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>25100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>25200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>24800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>32300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>27300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>31600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4839,103 +4968,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E57" s="3">
         <v>7100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>63900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>44900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>42100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>7200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -5029,79 +5162,82 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="E59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F59" s="3">
         <v>3600</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1100</v>
       </c>
       <c r="G59" s="3">
         <v>1100</v>
       </c>
       <c r="H59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1600</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1400</v>
       </c>
       <c r="M59" s="3">
         <v>1400</v>
       </c>
       <c r="N59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O59" s="3">
         <v>3500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>200</v>
-      </c>
-      <c r="V59" s="3">
-        <v>300</v>
       </c>
       <c r="W59" s="3">
         <v>300</v>
       </c>
       <c r="X59" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="Y59" s="3">
         <v>500</v>
       </c>
       <c r="Z59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AA59" s="3">
         <v>300</v>
@@ -5113,114 +5249,120 @@
         <v>300</v>
       </c>
       <c r="AD59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE59" s="3">
         <v>1000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>67300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>47500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>43000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>13200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>12600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>11000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
@@ -5314,16 +5456,19 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -5332,46 +5477,46 @@
         <v>0</v>
       </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>200</v>
       </c>
       <c r="J62" s="3">
         <v>200</v>
       </c>
       <c r="K62" s="3">
+        <v>200</v>
+      </c>
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>400</v>
-      </c>
-      <c r="M62" s="3">
-        <v>500</v>
       </c>
       <c r="N62" s="3">
         <v>500</v>
       </c>
       <c r="O62" s="3">
+        <v>500</v>
+      </c>
+      <c r="P62" s="3">
         <v>600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1100</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>91</v>
@@ -5388,8 +5533,8 @@
       <c r="Z62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5409,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5694,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E66" s="3">
         <v>12300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>69100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>49700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6204,88 +6374,91 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E72" s="3">
         <v>28800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>29100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>30500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>30800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>32000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>32700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>33400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>34600</v>
-      </c>
-      <c r="M72" s="3">
-        <v>35700</v>
       </c>
       <c r="N72" s="3">
         <v>35700</v>
       </c>
       <c r="O72" s="3">
+        <v>35700</v>
+      </c>
+      <c r="P72" s="3">
         <v>31800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>24900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15400</v>
-      </c>
-      <c r="AC72" s="3">
-        <v>15800</v>
       </c>
       <c r="AD72" s="3">
         <v>15800</v>
@@ -6294,13 +6467,16 @@
         <v>15800</v>
       </c>
       <c r="AF72" s="3">
+        <v>15800</v>
+      </c>
+      <c r="AG72" s="3">
         <v>15200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6584,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E76" s="3">
         <v>38600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>38900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>40400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>40100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>39800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>41000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>41700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>42400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43600</v>
-      </c>
-      <c r="M76" s="3">
-        <v>44700</v>
       </c>
       <c r="N76" s="3">
         <v>44700</v>
       </c>
       <c r="O76" s="3">
+        <v>44700</v>
+      </c>
+      <c r="P76" s="3">
         <v>40700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>33400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17700</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>18100</v>
       </c>
       <c r="AD76" s="3">
         <v>18100</v>
       </c>
       <c r="AE76" s="3">
+        <v>18100</v>
+      </c>
+      <c r="AF76" s="3">
         <v>18000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6774,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>91</v>
+      <c r="D81" s="3">
+        <v>-800</v>
       </c>
       <c r="E81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>3900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>6900</v>
       </c>
       <c r="P81" s="3">
         <v>6900</v>
       </c>
       <c r="Q81" s="3">
+        <v>6900</v>
+      </c>
+      <c r="R81" s="3">
         <v>3700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AC81" s="3">
-        <v>0</v>
-      </c>
       <c r="AD81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="3">
         <v>100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7004,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -7016,7 +7214,7 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -7034,7 +7232,7 @@
         <v>200</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -7046,7 +7244,7 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -7055,7 +7253,7 @@
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
@@ -7067,7 +7265,7 @@
         <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
@@ -7076,22 +7274,22 @@
         <v>200</v>
       </c>
       <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA83" s="3">
         <v>100</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>200</v>
       </c>
       <c r="AB83" s="3">
         <v>200</v>
       </c>
       <c r="AC83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD83" s="3">
         <v>100</v>
       </c>
       <c r="AE83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF83" s="3">
         <v>200</v>
@@ -7099,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7574,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>100</v>
       </c>
-      <c r="G89" s="3">
-        <v>-6200</v>
-      </c>
       <c r="H89" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-16600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>27900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>20100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4900</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7704,38 +7923,39 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-600</v>
       </c>
       <c r="G91" s="3">
         <v>-600</v>
       </c>
       <c r="H91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -7755,23 +7975,23 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
@@ -7788,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE91" s="3">
         <v>-100</v>
@@ -7799,8 +8019,11 @@
       <c r="AG91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -7989,91 +8215,94 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-500</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-100</v>
       </c>
       <c r="Q94" s="3">
         <v>-100</v>
       </c>
       <c r="R94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-100</v>
       </c>
       <c r="AE94" s="3">
         <v>-100</v>
@@ -8084,8 +8313,11 @@
       <c r="AG94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8119,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -8214,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8499,32 +8741,35 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>91</v>
+      <c r="D100" s="3">
+        <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -8541,13 +8786,13 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>6000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>91</v>
@@ -8555,14 +8800,14 @@
       <c r="T100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
+      <c r="U100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -8571,11 +8816,11 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
@@ -8586,39 +8831,42 @@
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
@@ -8630,23 +8878,23 @@
         <v>-100</v>
       </c>
       <c r="N101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
@@ -8669,119 +8917,125 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>100</v>
       </c>
       <c r="AG101" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>27700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>20500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E8" s="3">
         <v>8800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>44300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>66200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>62600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>37400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E9" s="3">
         <v>8000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>36800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>55000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>50900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>30500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>11200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>11500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>10400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
         <v>800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1600</v>
       </c>
       <c r="J10" s="3">
         <v>1600</v>
       </c>
       <c r="K10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L10" s="3">
         <v>1400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>1400</v>
       </c>
       <c r="AC10" s="3">
         <v>1400</v>
       </c>
       <c r="AD10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AE10" s="3">
         <v>2200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2900</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>2300</v>
       </c>
       <c r="AH10" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,13 +1138,14 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E12" s="3">
         <v>900</v>
@@ -1140,16 +1154,16 @@
         <v>900</v>
       </c>
       <c r="G12" s="3">
+        <v>900</v>
+      </c>
+      <c r="H12" s="3">
         <v>1100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1000</v>
       </c>
       <c r="I12" s="3">
         <v>1000</v>
       </c>
       <c r="J12" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="K12" s="3">
         <v>1100</v>
@@ -1158,10 +1172,10 @@
         <v>1100</v>
       </c>
       <c r="M12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N12" s="3">
         <v>1000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1200</v>
       </c>
       <c r="O12" s="3">
         <v>1200</v>
@@ -1170,40 +1184,40 @@
         <v>1200</v>
       </c>
       <c r="Q12" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="R12" s="3">
         <v>1000</v>
       </c>
       <c r="S12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T12" s="3">
         <v>800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>800</v>
-      </c>
-      <c r="W12" s="3">
-        <v>700</v>
       </c>
       <c r="X12" s="3">
         <v>700</v>
       </c>
       <c r="Y12" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z12" s="3">
         <v>800</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>700</v>
       </c>
       <c r="AA12" s="3">
         <v>700</v>
       </c>
       <c r="AB12" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AC12" s="3">
         <v>900</v>
@@ -1218,13 +1232,16 @@
         <v>900</v>
       </c>
       <c r="AG12" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AH12" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,52 +1338,55 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2400</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>91</v>
@@ -1383,8 +1403,8 @@
       <c r="V14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E17" s="3">
         <v>10400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>39100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>57000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>53400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>11800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5200</v>
-      </c>
-      <c r="P18" s="3">
-        <v>9200</v>
       </c>
       <c r="Q18" s="3">
         <v>9200</v>
       </c>
       <c r="R18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="S18" s="3">
         <v>4800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-700</v>
       </c>
-      <c r="AD18" s="3">
-        <v>0</v>
-      </c>
       <c r="AE18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>700</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>400</v>
       </c>
       <c r="AH18" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1782,62 +1815,63 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>200</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1851,19 +1885,19 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>100</v>
       </c>
       <c r="AD20" s="3">
         <v>100</v>
@@ -1875,111 +1909,117 @@
         <v>100</v>
       </c>
       <c r="AG20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5500</v>
-      </c>
-      <c r="P21" s="3">
-        <v>9300</v>
       </c>
       <c r="Q21" s="3">
         <v>9300</v>
       </c>
       <c r="R21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="S21" s="3">
         <v>5000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>-400</v>
       </c>
       <c r="AC21" s="3">
         <v>-400</v>
       </c>
       <c r="AD21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE21" s="3">
         <v>200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>100</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
       <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
         <v>800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
-      </c>
-      <c r="T24" s="3">
-        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>100</v>
       </c>
       <c r="V24" s="3">
+        <v>100</v>
+      </c>
+      <c r="W24" s="3">
         <v>-300</v>
-      </c>
-      <c r="W24" s="3">
-        <v>-100</v>
       </c>
       <c r="X24" s="3">
         <v>-100</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1100</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>4200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-400</v>
       </c>
-      <c r="AD26" s="3">
-        <v>0</v>
-      </c>
       <c r="AE26" s="3">
         <v>0</v>
       </c>
       <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3">
         <v>500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>3900</v>
-      </c>
-      <c r="P27" s="3">
-        <v>6900</v>
       </c>
       <c r="Q27" s="3">
         <v>6900</v>
       </c>
       <c r="R27" s="3">
+        <v>6900</v>
+      </c>
+      <c r="S27" s="3">
         <v>3700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>200</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-100</v>
       </c>
       <c r="AA27" s="3">
         <v>-100</v>
       </c>
       <c r="AB27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-400</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3">
         <v>100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,8 +2763,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>91</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>91</v>
@@ -2723,11 +2784,11 @@
       <c r="U29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="W29" s="3">
         <v>-100</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>91</v>
@@ -2735,11 +2796,11 @@
       <c r="Y29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-700</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>91</v>
@@ -2750,8 +2811,8 @@
       <c r="AD29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2958,62 +3025,65 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>-200</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3027,19 +3097,19 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-100</v>
       </c>
       <c r="AD32" s="3">
         <v>-100</v>
@@ -3051,111 +3121,117 @@
         <v>-100</v>
       </c>
       <c r="AG32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>3900</v>
-      </c>
-      <c r="P33" s="3">
-        <v>6900</v>
       </c>
       <c r="Q33" s="3">
         <v>6900</v>
       </c>
       <c r="R33" s="3">
+        <v>6900</v>
+      </c>
+      <c r="S33" s="3">
         <v>3700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-400</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3">
         <v>100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>3900</v>
-      </c>
-      <c r="P35" s="3">
-        <v>6900</v>
       </c>
       <c r="Q35" s="3">
         <v>6900</v>
       </c>
       <c r="R35" s="3">
+        <v>6900</v>
+      </c>
+      <c r="S35" s="3">
         <v>3700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-400</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3">
         <v>100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3525,135 +3611,139 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>39300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>45800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>54400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>71000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>28200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>14300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>10900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E42" s="3">
         <v>27500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>16400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>16600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>15300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6600</v>
-      </c>
-      <c r="L42" s="3">
-        <v>5400</v>
       </c>
       <c r="M42" s="3">
         <v>5400</v>
@@ -3685,8 +3775,8 @@
       <c r="V42" s="3">
         <v>5400</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>91</v>
+      <c r="W42" s="3">
+        <v>5400</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>91</v>
@@ -3700,8 +3790,8 @@
       <c r="AA42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -3721,204 +3811,213 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E43" s="3">
         <v>13700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>11100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>9600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>13800</v>
-      </c>
-      <c r="AG43" s="3">
-        <v>12400</v>
       </c>
       <c r="AH43" s="3">
         <v>12400</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>12400</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>11800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>800</v>
-      </c>
-      <c r="X44" s="3">
-        <v>1900</v>
       </c>
       <c r="Y44" s="3">
         <v>1900</v>
       </c>
       <c r="Z44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AA44" s="3">
         <v>1600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
@@ -3926,7 +4025,7 @@
         <v>200</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
@@ -3935,25 +4034,25 @@
         <v>100</v>
       </c>
       <c r="H45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3">
         <v>300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
       </c>
       <c r="J45" s="3">
         <v>200</v>
       </c>
       <c r="K45" s="3">
+        <v>200</v>
+      </c>
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>100</v>
       </c>
       <c r="O45" s="3">
         <v>100</v>
@@ -3965,7 +4064,7 @@
         <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45" s="3">
         <v>0</v>
@@ -3977,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3">
         <v>100</v>
@@ -3992,19 +4091,19 @@
         <v>100</v>
       </c>
       <c r="AA45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB45" s="3">
         <v>200</v>
       </c>
       <c r="AC45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD45" s="3">
         <v>100</v>
       </c>
       <c r="AE45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF45" s="3">
         <v>500</v>
@@ -4013,108 +4112,114 @@
         <v>500</v>
       </c>
       <c r="AH45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E46" s="3">
         <v>47800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>46100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>51900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>47300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>50400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>47000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>48400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>53300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>45500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>47200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>54800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>74400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>106100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>79400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>61400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>25300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>21600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>27600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>21700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>19900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>21900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>21200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>28900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>23900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>28100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>25900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>27900</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -4211,67 +4316,70 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E48" s="3">
         <v>100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>300</v>
       </c>
       <c r="H48" s="3">
+        <v>300</v>
+      </c>
+      <c r="I48" s="3">
         <v>400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>500</v>
-      </c>
-      <c r="J48" s="3">
-        <v>600</v>
       </c>
       <c r="K48" s="3">
         <v>600</v>
       </c>
       <c r="L48" s="3">
+        <v>600</v>
+      </c>
+      <c r="M48" s="3">
         <v>700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1500</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1600</v>
       </c>
       <c r="U48" s="3">
         <v>1600</v>
       </c>
       <c r="V48" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="W48" s="3">
         <v>100</v>
@@ -4289,7 +4397,7 @@
         <v>100</v>
       </c>
       <c r="AB48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC48" s="3">
         <v>200</v>
@@ -4301,7 +4409,7 @@
         <v>200</v>
       </c>
       <c r="AF48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG48" s="3">
         <v>300</v>
@@ -4309,106 +4417,112 @@
       <c r="AH48" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1900</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1600</v>
       </c>
       <c r="K49" s="3">
         <v>1600</v>
       </c>
       <c r="L49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M49" s="3">
         <v>1700</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1500</v>
       </c>
       <c r="N49" s="3">
         <v>1500</v>
       </c>
       <c r="O49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P49" s="3">
         <v>1600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1400</v>
       </c>
       <c r="R49" s="3">
         <v>1400</v>
       </c>
       <c r="S49" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="T49" s="3">
         <v>1500</v>
       </c>
       <c r="U49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V49" s="3">
         <v>1700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1400</v>
-      </c>
-      <c r="W49" s="3">
-        <v>1100</v>
       </c>
       <c r="X49" s="3">
         <v>1100</v>
       </c>
       <c r="Y49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z49" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>1300</v>
       </c>
       <c r="AA49" s="3">
         <v>1300</v>
       </c>
       <c r="AB49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC49" s="3">
         <v>1400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1400</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>1300</v>
       </c>
       <c r="AF49" s="3">
         <v>1300</v>
       </c>
       <c r="AG49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="AH49" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4603,94 +4720,97 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E52" s="3">
         <v>2600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2400</v>
       </c>
       <c r="F52" s="3">
         <v>2400</v>
       </c>
       <c r="G52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H52" s="3">
         <v>2000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2100</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>2000</v>
       </c>
       <c r="Z52" s="3">
         <v>2000</v>
       </c>
       <c r="AA52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB52" s="3">
         <v>1900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1800</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>1900</v>
       </c>
       <c r="AF52" s="3">
         <v>1900</v>
@@ -4699,10 +4819,13 @@
         <v>1900</v>
       </c>
       <c r="AH52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AI52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E54" s="3">
         <v>52600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>50900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>56900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>52400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>54600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>52000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>57200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>49400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>50500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>78000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>109700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>83100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>65400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>30300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>30800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>30800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>25200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>24800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>32300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>27300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>31600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>29500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
         <v>9100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>63900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>44900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>42100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>7200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -5165,82 +5299,85 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1100</v>
       </c>
       <c r="H59" s="3">
         <v>1100</v>
       </c>
       <c r="I59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1400</v>
       </c>
       <c r="N59" s="3">
         <v>1400</v>
       </c>
       <c r="O59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P59" s="3">
         <v>3500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>200</v>
-      </c>
-      <c r="W59" s="3">
-        <v>300</v>
       </c>
       <c r="X59" s="3">
         <v>300</v>
       </c>
       <c r="Y59" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="Z59" s="3">
         <v>500</v>
       </c>
       <c r="AA59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AB59" s="3">
         <v>300</v>
@@ -5252,117 +5389,123 @@
         <v>300</v>
       </c>
       <c r="AE59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF59" s="3">
         <v>1000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E60" s="3">
         <v>13000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>67300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>47500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>43000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>13200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>12600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>11000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
@@ -5459,19 +5602,22 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>91</v>
+      <c r="D62" s="3">
+        <v>1300</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G62" s="3">
         <v>0</v>
@@ -5480,46 +5626,46 @@
         <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>200</v>
       </c>
       <c r="K62" s="3">
         <v>200</v>
       </c>
       <c r="L62" s="3">
+        <v>200</v>
+      </c>
+      <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>400</v>
-      </c>
-      <c r="N62" s="3">
-        <v>500</v>
       </c>
       <c r="O62" s="3">
         <v>500</v>
       </c>
       <c r="P62" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q62" s="3">
         <v>600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1100</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>91</v>
@@ -5536,8 +5682,8 @@
       <c r="AA62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E66" s="3">
         <v>14500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>69100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>49700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6377,91 +6548,94 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E72" s="3">
         <v>28100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>30700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>30500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>30800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>32000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>32700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>34600</v>
-      </c>
-      <c r="N72" s="3">
-        <v>35700</v>
       </c>
       <c r="O72" s="3">
         <v>35700</v>
       </c>
       <c r="P72" s="3">
+        <v>35700</v>
+      </c>
+      <c r="Q72" s="3">
         <v>31800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>24900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>14700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15400</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>15800</v>
       </c>
       <c r="AE72" s="3">
         <v>15800</v>
@@ -6470,13 +6644,16 @@
         <v>15800</v>
       </c>
       <c r="AG72" s="3">
+        <v>15800</v>
+      </c>
+      <c r="AH72" s="3">
         <v>15200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E76" s="3">
         <v>38100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>38600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>38900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>40400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>40100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>39800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>41000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>42400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43600</v>
-      </c>
-      <c r="N76" s="3">
-        <v>44700</v>
       </c>
       <c r="O76" s="3">
         <v>44700</v>
       </c>
       <c r="P76" s="3">
+        <v>44700</v>
+      </c>
+      <c r="Q76" s="3">
         <v>40700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>33400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17700</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>18100</v>
       </c>
       <c r="AE76" s="3">
         <v>18100</v>
       </c>
       <c r="AF76" s="3">
+        <v>18100</v>
+      </c>
+      <c r="AG76" s="3">
         <v>18000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>3900</v>
-      </c>
-      <c r="P81" s="3">
-        <v>6900</v>
       </c>
       <c r="Q81" s="3">
         <v>6900</v>
       </c>
       <c r="R81" s="3">
+        <v>6900</v>
+      </c>
+      <c r="S81" s="3">
         <v>3700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-400</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
         <v>100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7202,13 +7400,14 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
@@ -7217,7 +7416,7 @@
         <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
@@ -7235,7 +7434,7 @@
         <v>200</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -7247,7 +7446,7 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
@@ -7256,7 +7455,7 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -7268,7 +7467,7 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
@@ -7277,22 +7476,22 @@
         <v>200</v>
       </c>
       <c r="AA83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB83" s="3">
         <v>100</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>200</v>
       </c>
       <c r="AC83" s="3">
         <v>200</v>
       </c>
       <c r="AD83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE83" s="3">
         <v>100</v>
       </c>
       <c r="AF83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG83" s="3">
         <v>200</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5200</v>
       </c>
-      <c r="F89" s="3">
-        <v>5200</v>
-      </c>
       <c r="G89" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-16600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>27900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>20100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4900</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
@@ -7933,32 +8154,32 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-600</v>
       </c>
       <c r="H91" s="3">
         <v>-600</v>
       </c>
       <c r="I91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -7978,23 +8199,23 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
@@ -8011,7 +8232,7 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF91" s="3">
         <v>-100</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8218,94 +8445,97 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O94" s="3">
         <v>-100</v>
       </c>
       <c r="P94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-100</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-100</v>
       </c>
       <c r="AF94" s="3">
         <v>-100</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
@@ -8756,23 +9002,23 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -8789,13 +9035,13 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>6000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>500</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>91</v>
@@ -8803,14 +9049,14 @@
       <c r="U100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
+      <c r="V100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -8819,11 +9065,11 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
@@ -8834,42 +9080,45 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>100</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>-100</v>
@@ -8881,23 +9130,23 @@
         <v>-100</v>
       </c>
       <c r="O101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
@@ -8920,122 +9169,128 @@
         <v>0</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>100</v>
       </c>
       <c r="AH101" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>27700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>20500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>FKWL</t>
   </si>
@@ -656,454 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F8" s="3">
         <v>6200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>8800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>9700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>17000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>11900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>9000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>12100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>6700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>11000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>44300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>66200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>62600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>37400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>15500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>13300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>8900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>5000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>9000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>9200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>13300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>7500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>6600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>8400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>7600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>11800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>9700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>14400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>12700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F9" s="3">
         <v>5700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>8000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>8100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>14600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>9800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>8000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>6500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>10500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>5300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>9000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>36800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>55000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>50900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>30500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>12500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>10700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>6800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>4300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>7400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>7900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>11200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>6600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>5100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>7000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>6200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>9600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>7800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>11500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>10400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>600</v>
+      </c>
+      <c r="F10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L10" s="3">
         <v>1600</v>
       </c>
-      <c r="G10" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="M10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O10" s="3">
+        <v>300</v>
+      </c>
+      <c r="P10" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R10" s="3">
+        <v>7500</v>
+      </c>
+      <c r="S10" s="3">
+        <v>11200</v>
+      </c>
+      <c r="T10" s="3">
+        <v>11700</v>
+      </c>
+      <c r="U10" s="3">
+        <v>6900</v>
+      </c>
+      <c r="V10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="W10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="X10" s="3">
         <v>2100</v>
       </c>
-      <c r="I10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="Y10" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1600</v>
       </c>
-      <c r="K10" s="3">
-        <v>1600</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="AA10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE10" s="3">
         <v>1400</v>
       </c>
-      <c r="M10" s="3">
-        <v>300</v>
-      </c>
-      <c r="N10" s="3">
-        <v>400</v>
-      </c>
-      <c r="O10" s="3">
-        <v>2000</v>
-      </c>
-      <c r="P10" s="3">
-        <v>7500</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>11200</v>
-      </c>
-      <c r="R10" s="3">
-        <v>11700</v>
-      </c>
-      <c r="S10" s="3">
-        <v>6900</v>
-      </c>
-      <c r="T10" s="3">
-        <v>3000</v>
-      </c>
-      <c r="U10" s="3">
-        <v>2600</v>
-      </c>
-      <c r="V10" s="3">
-        <v>2100</v>
-      </c>
-      <c r="W10" s="3">
-        <v>700</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>2100</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>900</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AF10" s="3">
         <v>1400</v>
       </c>
-      <c r="AD10" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>2200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>2900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>2300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,91 +1165,93 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E12" s="3">
         <v>900</v>
       </c>
       <c r="F12" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G12" s="3">
         <v>900</v>
       </c>
       <c r="H12" s="3">
+        <v>900</v>
+      </c>
+      <c r="I12" s="3">
+        <v>900</v>
+      </c>
+      <c r="J12" s="3">
         <v>1100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1100</v>
       </c>
       <c r="M12" s="3">
         <v>1100</v>
       </c>
       <c r="N12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P12" s="3">
         <v>1000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1200</v>
       </c>
       <c r="Q12" s="3">
         <v>1200</v>
       </c>
       <c r="R12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T12" s="3">
         <v>1000</v>
-      </c>
-      <c r="S12" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T12" s="3">
-        <v>800</v>
       </c>
       <c r="U12" s="3">
         <v>1000</v>
       </c>
       <c r="V12" s="3">
+        <v>800</v>
+      </c>
+      <c r="W12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X12" s="3">
         <v>900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>700</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>700</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>800</v>
       </c>
       <c r="AA12" s="3">
         <v>700</v>
       </c>
       <c r="AB12" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC12" s="3">
         <v>700</v>
       </c>
-      <c r="AC12" s="3">
-        <v>900</v>
-      </c>
       <c r="AD12" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AE12" s="3">
         <v>900</v>
@@ -1235,13 +1263,19 @@
         <v>900</v>
       </c>
       <c r="AH12" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>900</v>
+      </c>
+      <c r="AJ12" s="3">
         <v>800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,13 +1375,19 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1355,44 +1395,44 @@
       <c r="F14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="3">
         <v>2400</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-500</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>91</v>
@@ -1406,11 +1446,11 @@
       <c r="W14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1442,31 +1482,37 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1589,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F17" s="3">
         <v>7700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>10400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>10200</v>
       </c>
-      <c r="G17" s="3">
-        <v>19300</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>16900</v>
+      </c>
+      <c r="J17" s="3">
         <v>12300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>10200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>12600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>11300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>39100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>57000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>53400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>32600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>14300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>12500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>8600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>9400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>9900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>13200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>8600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>7000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>8900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>8300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>11800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>9800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>13700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>12300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-1500</v>
+        <v>-400</v>
       </c>
       <c r="E18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R18" s="3">
+        <v>5200</v>
+      </c>
+      <c r="S18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="T18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="U18" s="3">
+        <v>4800</v>
+      </c>
+      <c r="V18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W18" s="3">
+        <v>800</v>
+      </c>
+      <c r="X18" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="AA18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>5200</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>9200</v>
-      </c>
-      <c r="R18" s="3">
-        <v>9200</v>
-      </c>
-      <c r="S18" s="3">
-        <v>4800</v>
-      </c>
-      <c r="T18" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U18" s="3">
-        <v>800</v>
-      </c>
-      <c r="V18" s="3">
-        <v>300</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="Z18" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1816,68 +1882,70 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-100</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
         <v>200</v>
       </c>
       <c r="G20" s="3">
-        <v>300</v>
+        <v>-500</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>200</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1888,22 +1956,22 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>100</v>
       </c>
       <c r="AF20" s="3">
         <v>100</v>
@@ -1912,137 +1980,149 @@
         <v>100</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="P21" s="3">
         <v>-1400</v>
       </c>
-      <c r="E21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="Q21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="R21" s="3">
+        <v>5500</v>
+      </c>
+      <c r="S21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="T21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="U21" s="3">
+        <v>5000</v>
+      </c>
+      <c r="V21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X21" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AG21" s="3">
         <v>200</v>
       </c>
-      <c r="J21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>5500</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>9300</v>
-      </c>
-      <c r="R21" s="3">
-        <v>9300</v>
-      </c>
-      <c r="S21" s="3">
-        <v>5000</v>
-      </c>
-      <c r="T21" s="3">
-        <v>1500</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="AH21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI21" s="3">
         <v>1000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="AJ21" s="3">
         <v>500</v>
       </c>
-      <c r="W21" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>300</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>200</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>100</v>
-      </c>
-      <c r="AG21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AH21" s="3">
-        <v>500</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2119,210 +2199,228 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-2000</v>
       </c>
       <c r="H23" s="3">
         <v>-400</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="J23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>5400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>9100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>9200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>4800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>100</v>
       </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3">
         <v>800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-600</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-100</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>1200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>2100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>0</v>
       </c>
       <c r="AF24" s="3">
         <v>-100</v>
       </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI24" s="3">
         <v>300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2422,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1100</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>4200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>7000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>7200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-400</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>0</v>
-      </c>
       <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3">
         <v>500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>3900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>6900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>6900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>3700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-400</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3">
         <v>100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2725,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2766,11 +2888,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>91</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>91</v>
@@ -2787,26 +2909,26 @@
       <c r="V29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="W29" s="3">
-        <v>-100</v>
+      <c r="W29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>91</v>
+      <c r="Y29" s="3">
+        <v>-100</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AA29" s="3">
-        <v>-700</v>
+      <c r="AA29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>91</v>
+      <c r="AC29" s="3">
+        <v>-700</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>91</v>
@@ -2814,11 +2936,11 @@
       <c r="AE29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
@@ -2826,8 +2948,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2927,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3028,68 +3162,74 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
-        <v>-700</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
         <v>-200</v>
       </c>
       <c r="G32" s="3">
-        <v>-300</v>
+        <v>500</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3100,22 +3240,22 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>100</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-100</v>
       </c>
       <c r="AF32" s="3">
         <v>-100</v>
@@ -3124,114 +3264,126 @@
         <v>-100</v>
       </c>
       <c r="AH32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1100</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>3900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>6900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>6900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
         <v>100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3331,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1100</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>3900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>6900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>6900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3">
         <v>100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3575,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3612,144 +3784,152 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F41" s="3">
         <v>7000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>12200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>17900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>25500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>26300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>36500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>36700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>39300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>45800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>54400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>71000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>43300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>28200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>7600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>9400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>6400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>10800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>12600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>16800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>12000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>12100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>13500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>11800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>14300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>12500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>11700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>10900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>25200</v>
+      </c>
+      <c r="F42" s="3">
         <v>24700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>27500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>26800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>26700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>16400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>16600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>15300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>16300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>6600</v>
-      </c>
-      <c r="M42" s="3">
-        <v>5400</v>
-      </c>
-      <c r="N42" s="3">
-        <v>5400</v>
       </c>
       <c r="O42" s="3">
         <v>5400</v>
@@ -3778,11 +3958,11 @@
       <c r="W42" s="3">
         <v>5400</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>91</v>
+      <c r="X42" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>5400</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>91</v>
@@ -3793,11 +3973,11 @@
       <c r="AB42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -3814,210 +3994,228 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F43" s="3">
         <v>10500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>13700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>10000</v>
       </c>
-      <c r="G43" s="3">
-        <v>9100</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J43" s="3">
         <v>7300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>8200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>13200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>16400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>27900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>16000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>11300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>7500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>8200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>8000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>7100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>8800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>8100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>6300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>6800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>7400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>11100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>9600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>13800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>12400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F44" s="3">
         <v>1100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>3700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>7400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>4200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>7700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>13200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>11800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>2200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>3400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>2200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>2100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
@@ -4028,37 +4226,37 @@
         <v>200</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H45" s="3">
         <v>100</v>
       </c>
       <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
-      </c>
-      <c r="M45" s="3">
-        <v>100</v>
-      </c>
-      <c r="N45" s="3">
-        <v>200</v>
       </c>
       <c r="O45" s="3">
         <v>100</v>
       </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
@@ -4067,10 +4265,10 @@
         <v>100</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -4079,10 +4277,10 @@
         <v>0</v>
       </c>
       <c r="W45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>100</v>
@@ -4094,155 +4292,167 @@
         <v>100</v>
       </c>
       <c r="AB45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>100</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>500</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>500</v>
       </c>
       <c r="AH45" s="3">
         <v>500</v>
       </c>
       <c r="AI45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AK45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>40200</v>
+      </c>
+      <c r="F46" s="3">
         <v>43500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>47800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>46100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>51900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>47300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>50400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>47000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>48400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>53300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>45500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>47200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>54800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>74400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>106100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>79400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>61400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>25100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>25300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>20700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>17100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>19600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>21600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>27600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>21700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>19900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>21900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>21200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>28900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>23900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>28100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>25900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>27900</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,8 +4529,14 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
@@ -4328,64 +4544,64 @@
         <v>1700</v>
       </c>
       <c r="E48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G48" s="3">
         <v>100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1600</v>
-      </c>
-      <c r="W48" s="3">
-        <v>100</v>
-      </c>
-      <c r="X48" s="3">
-        <v>100</v>
       </c>
       <c r="Y48" s="3">
         <v>100</v>
@@ -4400,10 +4616,10 @@
         <v>100</v>
       </c>
       <c r="AC48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE48" s="3">
         <v>200</v>
@@ -4412,117 +4628,129 @@
         <v>200</v>
       </c>
       <c r="AG48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AH48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AI48" s="3">
         <v>300</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK48" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F49" s="3">
         <v>1900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1300</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>1500</v>
       </c>
       <c r="AE49" s="3">
         <v>1400</v>
       </c>
       <c r="AF49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AH49" s="3">
         <v>1300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>1300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>1400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4622,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4723,31 +4957,37 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>2900</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>2600</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>2400</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>2400</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>1500</v>
@@ -4759,73 +4999,79 @@
         <v>1500</v>
       </c>
       <c r="N52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2000</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>1900</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>1700</v>
       </c>
       <c r="AD52" s="3">
         <v>1900</v>
       </c>
       <c r="AE52" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="AF52" s="3">
         <v>1900</v>
       </c>
       <c r="AG52" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="AH52" s="3">
         <v>1900</v>
       </c>
       <c r="AI52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AJ52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AK52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -4925,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>46700</v>
+      </c>
+      <c r="F54" s="3">
         <v>50000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>52600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>50900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>56900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>52400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>54600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>51000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>52000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>57200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>49400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>50500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>57800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>78000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>109700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>83100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>65400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>30300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>30800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>26600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>21200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>23100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>24900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>30800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>25100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>23300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>25200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>24800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>32300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>27300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>31600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>29500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5063,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5100,132 +5360,140 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F57" s="3">
         <v>6300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>13000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>9300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>11900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>8100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>12300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>9700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>27900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>63900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>44900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>42100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>11400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>12900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>9100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>6600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>8200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>13200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>7600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>5100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>7000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>5800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>12900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>7200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>11800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>10600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5302,88 +5570,94 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>4200</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
-        <v>3900</v>
+        <v>200</v>
       </c>
       <c r="F59" s="3">
-        <v>3700</v>
+        <v>2600</v>
       </c>
       <c r="G59" s="3">
-        <v>3600</v>
+        <v>2700</v>
       </c>
       <c r="H59" s="3">
-        <v>1100</v>
+        <v>2700</v>
       </c>
       <c r="I59" s="3">
-        <v>1100</v>
+        <v>2600</v>
       </c>
       <c r="J59" s="3">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="K59" s="3">
         <v>1100</v>
       </c>
       <c r="L59" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="M59" s="3">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="N59" s="3">
         <v>1400</v>
       </c>
       <c r="O59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R59" s="3">
         <v>3500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>900</v>
-      </c>
-      <c r="T59" s="3">
-        <v>800</v>
-      </c>
-      <c r="U59" s="3">
-        <v>600</v>
       </c>
       <c r="V59" s="3">
         <v>800</v>
       </c>
       <c r="W59" s="3">
+        <v>600</v>
+      </c>
+      <c r="X59" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y59" s="3">
         <v>200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>500</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>300</v>
       </c>
       <c r="AD59" s="3">
         <v>300</v>
@@ -5392,131 +5666,143 @@
         <v>300</v>
       </c>
       <c r="AF59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH59" s="3">
         <v>1000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F60" s="3">
         <v>10400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>13000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>16500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>13000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>9300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>13700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>5000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>11200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>31300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>67300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>47500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>43000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>12200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>13500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>9900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>5900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>7000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>8600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>13700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>8100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>5400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>7200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>6100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>13200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>8200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>12600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>11000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -5605,13 +5891,19 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="3">
-        <v>1300</v>
+      <c r="D62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>91</v>
@@ -5619,59 +5911,59 @@
       <c r="F62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1100</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>91</v>
@@ -5685,11 +5977,11 @@
       <c r="AB62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
@@ -5706,8 +5998,14 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -5807,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5908,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6009,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>13200</v>
+        <v>14400</v>
       </c>
       <c r="E66" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F66" s="3">
+        <v>11800</v>
+      </c>
+      <c r="G66" s="3">
+        <v>13000</v>
+      </c>
+      <c r="H66" s="3">
+        <v>10800</v>
+      </c>
+      <c r="I66" s="3">
+        <v>16500</v>
+      </c>
+      <c r="J66" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K66" s="3">
+        <v>14600</v>
+      </c>
+      <c r="L66" s="3">
+        <v>11200</v>
+      </c>
+      <c r="M66" s="3">
+        <v>11000</v>
+      </c>
+      <c r="N66" s="3">
+        <v>15400</v>
+      </c>
+      <c r="O66" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P66" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>13100</v>
+      </c>
+      <c r="R66" s="3">
+        <v>33300</v>
+      </c>
+      <c r="S66" s="3">
+        <v>69100</v>
+      </c>
+      <c r="T66" s="3">
+        <v>49700</v>
+      </c>
+      <c r="U66" s="3">
+        <v>45000</v>
+      </c>
+      <c r="V66" s="3">
+        <v>13700</v>
+      </c>
+      <c r="W66" s="3">
+        <v>15200</v>
+      </c>
+      <c r="X66" s="3">
+        <v>11600</v>
+      </c>
+      <c r="Y66" s="3">
+        <v>6400</v>
+      </c>
+      <c r="Z66" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AB66" s="3">
         <v>14500</v>
       </c>
-      <c r="F66" s="3">
-        <v>12300</v>
-      </c>
-      <c r="G66" s="3">
-        <v>18000</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="AC66" s="3">
+        <v>9000</v>
+      </c>
+      <c r="AD66" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AE66" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AF66" s="3">
+        <v>7100</v>
+      </c>
+      <c r="AG66" s="3">
+        <v>14200</v>
+      </c>
+      <c r="AH66" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AI66" s="3">
+        <v>13600</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>12000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="AK66" s="3">
         <v>14600</v>
       </c>
-      <c r="J66" s="3">
-        <v>11200</v>
-      </c>
-      <c r="K66" s="3">
-        <v>11000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>15400</v>
-      </c>
-      <c r="M66" s="3">
-        <v>7000</v>
-      </c>
-      <c r="N66" s="3">
-        <v>6900</v>
-      </c>
-      <c r="O66" s="3">
-        <v>13100</v>
-      </c>
-      <c r="P66" s="3">
-        <v>33300</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>69100</v>
-      </c>
-      <c r="R66" s="3">
-        <v>49700</v>
-      </c>
-      <c r="S66" s="3">
-        <v>45000</v>
-      </c>
-      <c r="T66" s="3">
-        <v>13700</v>
-      </c>
-      <c r="U66" s="3">
-        <v>15200</v>
-      </c>
-      <c r="V66" s="3">
-        <v>11600</v>
-      </c>
-      <c r="W66" s="3">
-        <v>6400</v>
-      </c>
-      <c r="X66" s="3">
-        <v>7500</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>9200</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>14500</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>9000</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>6300</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>8200</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>7100</v>
-      </c>
-      <c r="AE66" s="3">
-        <v>14200</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>9200</v>
-      </c>
-      <c r="AG66" s="3">
-        <v>13600</v>
-      </c>
-      <c r="AH66" s="3">
-        <v>12000</v>
-      </c>
-      <c r="AI66" s="3">
-        <v>14600</v>
-      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6147,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6248,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6349,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6450,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6551,109 +6893,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>25100</v>
+      </c>
+      <c r="F72" s="3">
         <v>26900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>28100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>28800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>29100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>30700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>30500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>30800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>32000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>32700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>33400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>34600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>35700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>35700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>31800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>24900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>18000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>14300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>13300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>12700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>12500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>13300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>13400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>13900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>13800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>14500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>14700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>15400</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>15800</v>
-      </c>
-      <c r="AF72" s="3">
-        <v>15800</v>
       </c>
       <c r="AG72" s="3">
         <v>15800</v>
       </c>
       <c r="AH72" s="3">
+        <v>15800</v>
+      </c>
+      <c r="AI72" s="3">
+        <v>15800</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>15200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -6753,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -6854,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -6955,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>35100</v>
+      </c>
+      <c r="F76" s="3">
         <v>36900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>38100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>38600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>38900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>40400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>40100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>39800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>41000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>41700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>42400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>43600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>44700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>44700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>40700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>33400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>20400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>16600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>15600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>15000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>14800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>15600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>15800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>16300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>16100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>16900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>17000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>17700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>18100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>18100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>18000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>17500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7157,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1100</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>3900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>6900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>6900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3">
         <v>100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7401,31 +7797,33 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -7437,10 +7835,10 @@
         <v>200</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -7449,19 +7847,19 @@
         <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
@@ -7470,40 +7868,46 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA83" s="3">
         <v>200</v>
       </c>
       <c r="AB83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC83" s="3">
         <v>200</v>
       </c>
       <c r="AD83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE83" s="3">
         <v>200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG83" s="3">
         <v>100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>100</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>200</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>200</v>
       </c>
       <c r="AI83" s="3">
         <v>200</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK83" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -7603,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -7704,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -7805,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -7906,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8007,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-5200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-6100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-6400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-8400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>27900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>9200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>20100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>4500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>4900</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8145,83 +8585,85 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="O91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
@@ -8235,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH91" s="3">
         <v>-100</v>
@@ -8246,8 +8688,14 @@
       <c r="AI91" s="3">
         <v>-100</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8347,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8448,100 +8902,106 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F94" s="3">
         <v>2700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-10400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-9900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-500</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-200</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
       </c>
       <c r="V94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-5800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>-100</v>
       </c>
       <c r="AH94" s="3">
         <v>-100</v>
@@ -8549,8 +9009,14 @@
       <c r="AI94" s="3">
         <v>-100</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK94" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -8586,31 +9052,33 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +9155,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -8788,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -8889,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -8990,28 +9476,34 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -9023,7 +9515,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9038,22 +9530,22 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>6000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>500</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>91</v>
@@ -9061,21 +9553,21 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
@@ -9083,16 +9575,22 @@
         <v>0</v>
       </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>100</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
@@ -9100,31 +9598,31 @@
         <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3">
         <v>-100</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-100</v>
       </c>
       <c r="N101" s="3">
         <v>-100</v>
@@ -9133,26 +9631,26 @@
         <v>-100</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
@@ -9172,125 +9670,137 @@
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH101" s="3">
         <v>100</v>
       </c>
       <c r="AI101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>100</v>
       </c>
+      <c r="AK101" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-7600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-10200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-6500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-8600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-16700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>27700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>15200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>20500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>4400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-4300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>4800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>1700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>FKWL</t>
   </si>
@@ -656,480 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E8" s="3">
         <v>13300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>44300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>66200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>62600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>37400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>15500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>11800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>14400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E9" s="3">
         <v>11300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>36800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>55000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>50900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>30500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>11200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>9600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>11500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>10400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1600</v>
       </c>
       <c r="M10" s="3">
         <v>1600</v>
       </c>
       <c r="N10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O10" s="3">
         <v>1400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1500</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>1400</v>
       </c>
       <c r="AF10" s="3">
         <v>1400</v>
       </c>
       <c r="AG10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AH10" s="3">
         <v>2200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2900</v>
-      </c>
-      <c r="AJ10" s="3">
-        <v>2300</v>
       </c>
       <c r="AK10" s="3">
         <v>2300</v>
       </c>
+      <c r="AL10" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,22 +1179,23 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3">
         <v>1000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>800</v>
-      </c>
-      <c r="G12" s="3">
-        <v>900</v>
       </c>
       <c r="H12" s="3">
         <v>900</v>
@@ -1191,16 +1204,16 @@
         <v>900</v>
       </c>
       <c r="J12" s="3">
+        <v>900</v>
+      </c>
+      <c r="K12" s="3">
         <v>1100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1000</v>
       </c>
       <c r="L12" s="3">
         <v>1000</v>
       </c>
       <c r="M12" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="N12" s="3">
         <v>1100</v>
@@ -1209,10 +1222,10 @@
         <v>1100</v>
       </c>
       <c r="P12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q12" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1200</v>
       </c>
       <c r="R12" s="3">
         <v>1200</v>
@@ -1221,40 +1234,40 @@
         <v>1200</v>
       </c>
       <c r="T12" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="U12" s="3">
         <v>1000</v>
       </c>
       <c r="V12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W12" s="3">
         <v>800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>800</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>700</v>
       </c>
       <c r="AA12" s="3">
         <v>700</v>
       </c>
       <c r="AB12" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC12" s="3">
         <v>800</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>700</v>
       </c>
       <c r="AD12" s="3">
         <v>700</v>
       </c>
       <c r="AE12" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AF12" s="3">
         <v>900</v>
@@ -1269,13 +1282,16 @@
         <v>900</v>
       </c>
       <c r="AJ12" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AK12" s="3">
         <v>800</v>
       </c>
+      <c r="AL12" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1381,19 +1397,22 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="3">
         <v>-200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>91</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>91</v>
@@ -1401,41 +1420,41 @@
       <c r="H14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="3">
         <v>2400</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-500</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>91</v>
@@ -1452,8 +1471,8 @@
       <c r="Y14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1488,22 +1507,25 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
       </c>
       <c r="F15" s="3">
+        <v>300</v>
+      </c>
+      <c r="G15" s="3">
         <v>200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>300</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
@@ -1512,11 +1534,11 @@
         <v>300</v>
       </c>
       <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>39100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>57000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>53400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>11800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>13700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>12300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2200</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1600</v>
       </c>
       <c r="G18" s="3">
         <v>-1600</v>
       </c>
       <c r="H18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5200</v>
-      </c>
-      <c r="S18" s="3">
-        <v>9200</v>
       </c>
       <c r="T18" s="3">
         <v>9200</v>
       </c>
       <c r="U18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="V18" s="3">
         <v>4800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-700</v>
       </c>
-      <c r="AG18" s="3">
-        <v>0</v>
-      </c>
       <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>700</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>400</v>
       </c>
       <c r="AK18" s="3">
         <v>400</v>
       </c>
+      <c r="AL18" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1884,71 +1916,72 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>200</v>
       </c>
       <c r="F20" s="3">
         <v>200</v>
       </c>
       <c r="G20" s="3">
+        <v>200</v>
+      </c>
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1962,19 +1995,19 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>100</v>
       </c>
       <c r="AG20" s="3">
         <v>100</v>
@@ -1986,120 +2019,126 @@
         <v>100</v>
       </c>
       <c r="AJ20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
         <v>500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5500</v>
-      </c>
-      <c r="S21" s="3">
-        <v>9300</v>
       </c>
       <c r="T21" s="3">
         <v>9300</v>
       </c>
       <c r="U21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="V21" s="3">
         <v>5000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>-400</v>
       </c>
       <c r="AF21" s="3">
         <v>-400</v>
       </c>
       <c r="AG21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AH21" s="3">
         <v>200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2124,8 +2163,8 @@
       <c r="J22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2205,222 +2244,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>-1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>9100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>100</v>
       </c>
-      <c r="AH23" s="3">
-        <v>0</v>
-      </c>
       <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
-      </c>
-      <c r="W24" s="3">
-        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
       </c>
       <c r="Y24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>-100</v>
       </c>
       <c r="AA24" s="3">
         <v>-100</v>
       </c>
       <c r="AB24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-100</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2526,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>4200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-400</v>
       </c>
-      <c r="AG26" s="3">
-        <v>0</v>
-      </c>
       <c r="AH26" s="3">
         <v>0</v>
       </c>
       <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>3900</v>
-      </c>
-      <c r="S27" s="3">
-        <v>6900</v>
       </c>
       <c r="T27" s="3">
         <v>6900</v>
       </c>
       <c r="U27" s="3">
+        <v>6900</v>
+      </c>
+      <c r="V27" s="3">
         <v>3700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>200</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-100</v>
       </c>
       <c r="AD27" s="3">
         <v>-100</v>
       </c>
       <c r="AE27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-400</v>
       </c>
-      <c r="AG27" s="3">
-        <v>0</v>
-      </c>
       <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3">
         <v>100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2847,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2894,8 +2954,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>91</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>91</v>
@@ -2915,11 +2975,11 @@
       <c r="X29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>91</v>
@@ -2927,11 +2987,11 @@
       <c r="AB29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>91</v>
@@ -2942,8 +3002,8 @@
       <c r="AG29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
+      <c r="AH29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AI29" s="3">
         <v>0</v>
@@ -2954,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3061,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3168,71 +3234,74 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-200</v>
       </c>
       <c r="F32" s="3">
         <v>-200</v>
       </c>
       <c r="G32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -3246,19 +3315,19 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>100</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-100</v>
       </c>
       <c r="AG32" s="3">
         <v>-100</v>
@@ -3270,120 +3339,126 @@
         <v>-100</v>
       </c>
       <c r="AJ32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>3900</v>
-      </c>
-      <c r="S33" s="3">
-        <v>6900</v>
       </c>
       <c r="T33" s="3">
         <v>6900</v>
       </c>
       <c r="U33" s="3">
+        <v>6900</v>
+      </c>
+      <c r="V33" s="3">
         <v>3700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-400</v>
       </c>
-      <c r="AG33" s="3">
-        <v>0</v>
-      </c>
       <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
         <v>100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3489,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>3900</v>
-      </c>
-      <c r="S35" s="3">
-        <v>6900</v>
       </c>
       <c r="T35" s="3">
         <v>6900</v>
       </c>
       <c r="U35" s="3">
+        <v>6900</v>
+      </c>
+      <c r="V35" s="3">
         <v>3700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-400</v>
       </c>
-      <c r="AG35" s="3">
-        <v>0</v>
-      </c>
       <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3">
         <v>100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3747,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3786,153 +3871,157 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E41" s="3">
         <v>14600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>39300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>54400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>71000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>43300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>28200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>14300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>12500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>10900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E42" s="3">
         <v>26100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>24700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>16600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>16300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6600</v>
-      </c>
-      <c r="O42" s="3">
-        <v>5400</v>
       </c>
       <c r="P42" s="3">
         <v>5400</v>
@@ -3964,8 +4053,8 @@
       <c r="Y42" s="3">
         <v>5400</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>91</v>
+      <c r="Z42" s="3">
+        <v>5400</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>91</v>
@@ -3979,8 +4068,8 @@
       <c r="AD42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -4000,227 +4089,236 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>27900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>11100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>9600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>13800</v>
-      </c>
-      <c r="AJ43" s="3">
-        <v>12400</v>
       </c>
       <c r="AK43" s="3">
         <v>12400</v>
       </c>
+      <c r="AL43" s="3">
+        <v>12400</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E44" s="3">
         <v>2600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>11800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>800</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>1900</v>
       </c>
       <c r="AB44" s="3">
         <v>1900</v>
       </c>
       <c r="AC44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AD44" s="3">
         <v>1600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
         <v>200</v>
@@ -4232,7 +4330,7 @@
         <v>200</v>
       </c>
       <c r="H45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I45" s="3">
         <v>100</v>
@@ -4241,25 +4339,25 @@
         <v>100</v>
       </c>
       <c r="K45" s="3">
+        <v>100</v>
+      </c>
+      <c r="L45" s="3">
         <v>300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>200</v>
       </c>
       <c r="M45" s="3">
         <v>200</v>
       </c>
       <c r="N45" s="3">
+        <v>200</v>
+      </c>
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
@@ -4271,7 +4369,7 @@
         <v>100</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -4283,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="Y45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3">
         <v>100</v>
@@ -4298,19 +4396,19 @@
         <v>100</v>
       </c>
       <c r="AD45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE45" s="3">
         <v>200</v>
       </c>
       <c r="AF45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG45" s="3">
         <v>100</v>
       </c>
       <c r="AH45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AI45" s="3">
         <v>500</v>
@@ -4319,117 +4417,123 @@
         <v>500</v>
       </c>
       <c r="AK45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AL45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E46" s="3">
         <v>45300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>40200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>47800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>46100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>51900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>47300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>50400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>47000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>48400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>53300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>45500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>47200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>54800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>74400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>106100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>79400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>61400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>25100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>25300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>20700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>21600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>27600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>21700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>19900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>21900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>21200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>28900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>23900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>28100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>25900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>27900</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -4454,8 +4558,8 @@
       <c r="J47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4535,76 +4639,79 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>300</v>
       </c>
       <c r="J48" s="3">
         <v>300</v>
       </c>
       <c r="K48" s="3">
+        <v>300</v>
+      </c>
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>500</v>
-      </c>
-      <c r="M48" s="3">
-        <v>600</v>
       </c>
       <c r="N48" s="3">
         <v>600</v>
       </c>
       <c r="O48" s="3">
+        <v>600</v>
+      </c>
+      <c r="P48" s="3">
         <v>700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1500</v>
-      </c>
-      <c r="W48" s="3">
-        <v>1600</v>
       </c>
       <c r="X48" s="3">
         <v>1600</v>
       </c>
       <c r="Y48" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="Z48" s="3">
         <v>100</v>
@@ -4622,7 +4729,7 @@
         <v>100</v>
       </c>
       <c r="AE48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF48" s="3">
         <v>200</v>
@@ -4634,7 +4741,7 @@
         <v>200</v>
       </c>
       <c r="AI48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AJ48" s="3">
         <v>300</v>
@@ -4642,115 +4749,121 @@
       <c r="AK48" s="3">
         <v>300</v>
       </c>
+      <c r="AL48" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1900</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1600</v>
       </c>
       <c r="N49" s="3">
         <v>1600</v>
       </c>
       <c r="O49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P49" s="3">
         <v>1700</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1500</v>
       </c>
       <c r="Q49" s="3">
         <v>1500</v>
       </c>
       <c r="R49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S49" s="3">
         <v>1600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1700</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1400</v>
       </c>
       <c r="U49" s="3">
         <v>1400</v>
       </c>
       <c r="V49" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="W49" s="3">
         <v>1500</v>
       </c>
       <c r="X49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y49" s="3">
         <v>1700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>1100</v>
       </c>
       <c r="AA49" s="3">
         <v>1100</v>
       </c>
       <c r="AB49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC49" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>1300</v>
       </c>
       <c r="AD49" s="3">
         <v>1300</v>
       </c>
       <c r="AE49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AF49" s="3">
         <v>1400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1400</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>1300</v>
       </c>
       <c r="AI49" s="3">
         <v>1300</v>
       </c>
       <c r="AJ49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="AK49" s="3">
         <v>1400</v>
       </c>
+      <c r="AL49" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4856,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -4963,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -4990,76 +5109,76 @@
         <v>100</v>
       </c>
       <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2100</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>2000</v>
       </c>
       <c r="AC52" s="3">
         <v>2000</v>
       </c>
       <c r="AD52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AE52" s="3">
         <v>1900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1800</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>1900</v>
       </c>
       <c r="AI52" s="3">
         <v>1900</v>
@@ -5068,10 +5187,13 @@
         <v>1900</v>
       </c>
       <c r="AK52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AL52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5177,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E54" s="3">
         <v>51600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>46700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>50000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>52600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>50900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>56900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>52400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>54600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>51000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>52000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>49400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>50500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>57800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>78000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>109700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>83100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>65400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>30300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>30800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>26600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>21200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>24900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>25100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>23300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>25200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>24800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>32300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>27300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>31600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>29500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5323,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5362,141 +5491,145 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E57" s="3">
         <v>10800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>63900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>44900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>42100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>7000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>7200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
-      </c>
-      <c r="E58" s="3">
-        <v>200</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>200</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5576,8 +5709,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
@@ -5588,79 +5724,79 @@
         <v>200</v>
       </c>
       <c r="F59" s="3">
+        <v>200</v>
+      </c>
+      <c r="G59" s="3">
         <v>2600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2700</v>
       </c>
       <c r="H59" s="3">
         <v>2700</v>
       </c>
       <c r="I59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1400</v>
       </c>
       <c r="Q59" s="3">
         <v>1400</v>
       </c>
       <c r="R59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S59" s="3">
         <v>3500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>200</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>300</v>
       </c>
       <c r="AA59" s="3">
         <v>300</v>
       </c>
       <c r="AB59" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AC59" s="3">
         <v>500</v>
       </c>
       <c r="AD59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AE59" s="3">
         <v>300</v>
@@ -5672,131 +5808,137 @@
         <v>300</v>
       </c>
       <c r="AH59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI59" s="3">
         <v>1000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E60" s="3">
         <v>13100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>31300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>67300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>47500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>43000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>11000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E61" s="3">
         <v>1300</v>
@@ -5805,7 +5947,7 @@
         <v>1300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -5897,8 +6039,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
@@ -5923,50 +6068,50 @@
       <c r="J62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>200</v>
       </c>
       <c r="N62" s="3">
         <v>200</v>
       </c>
       <c r="O62" s="3">
+        <v>200</v>
+      </c>
+      <c r="P62" s="3">
         <v>300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>400</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>500</v>
       </c>
       <c r="R62" s="3">
         <v>500</v>
       </c>
       <c r="S62" s="3">
+        <v>500</v>
+      </c>
+      <c r="T62" s="3">
         <v>600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>91</v>
@@ -5983,8 +6128,8 @@
       <c r="AD62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -6004,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6111,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6218,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6325,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E66" s="3">
         <v>14400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>33300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>69100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>49700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>45000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6471,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6578,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6685,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6792,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -6899,100 +7069,103 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E72" s="3">
         <v>25700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>26900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>29100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>30700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>32000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>32700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>33400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>34600</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>35700</v>
       </c>
       <c r="R72" s="3">
         <v>35700</v>
       </c>
       <c r="S72" s="3">
+        <v>35700</v>
+      </c>
+      <c r="T72" s="3">
         <v>31800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>24900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>14500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15400</v>
-      </c>
-      <c r="AG72" s="3">
-        <v>15800</v>
       </c>
       <c r="AH72" s="3">
         <v>15800</v>
@@ -7001,13 +7174,16 @@
         <v>15800</v>
       </c>
       <c r="AJ72" s="3">
+        <v>15800</v>
+      </c>
+      <c r="AK72" s="3">
         <v>15200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7113,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7220,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7327,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E76" s="3">
         <v>35800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>36900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>38100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>38600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>38900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>40400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>40100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>39800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>41000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>42400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>43600</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>44700</v>
       </c>
       <c r="R76" s="3">
         <v>44700</v>
       </c>
       <c r="S76" s="3">
+        <v>44700</v>
+      </c>
+      <c r="T76" s="3">
         <v>40700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>33400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>16100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>16900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17700</v>
-      </c>
-      <c r="AG76" s="3">
-        <v>18100</v>
       </c>
       <c r="AH76" s="3">
         <v>18100</v>
       </c>
       <c r="AI76" s="3">
+        <v>18100</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>17500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7541,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>200</v>
+      </c>
+      <c r="E81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>3900</v>
-      </c>
-      <c r="S81" s="3">
-        <v>6900</v>
       </c>
       <c r="T81" s="3">
         <v>6900</v>
       </c>
       <c r="U81" s="3">
+        <v>6900</v>
+      </c>
+      <c r="V81" s="3">
         <v>3700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-400</v>
       </c>
-      <c r="AG81" s="3">
-        <v>0</v>
-      </c>
       <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3">
         <v>100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7799,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -7826,7 +8024,7 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
@@ -7841,7 +8039,7 @@
         <v>200</v>
       </c>
       <c r="P83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
@@ -7853,7 +8051,7 @@
         <v>100</v>
       </c>
       <c r="T83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
@@ -7862,7 +8060,7 @@
         <v>200</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>100</v>
@@ -7874,7 +8072,7 @@
         <v>100</v>
       </c>
       <c r="AA83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB83" s="3">
         <v>200</v>
@@ -7883,22 +8081,22 @@
         <v>200</v>
       </c>
       <c r="AD83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE83" s="3">
         <v>100</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>200</v>
       </c>
       <c r="AF83" s="3">
         <v>200</v>
       </c>
       <c r="AG83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH83" s="3">
         <v>100</v>
       </c>
       <c r="AI83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AJ83" s="3">
         <v>200</v>
@@ -7906,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>200</v>
       </c>
+      <c r="AL83" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8013,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8120,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8227,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8334,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8441,8 +8654,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
@@ -8450,106 +8666,109 @@
         <v>2700</v>
       </c>
       <c r="E89" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F89" s="3">
         <v>6200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-16600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>27900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>20100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4900</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
       <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8587,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
@@ -8614,23 +8834,23 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -8650,23 +8870,23 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X91" s="3">
         <v>-100</v>
       </c>
       <c r="Y91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
@@ -8683,7 +8903,7 @@
         <v>0</v>
       </c>
       <c r="AH91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI91" s="3">
         <v>-100</v>
@@ -8694,8 +8914,11 @@
       <c r="AK91" s="3">
         <v>-100</v>
       </c>
+      <c r="AL91" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -8801,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -8908,103 +9134,106 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T94" s="3">
         <v>-500</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
       </c>
       <c r="V94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AH94" s="3">
-        <v>-100</v>
       </c>
       <c r="AI94" s="3">
         <v>-100</v>
@@ -9015,8 +9244,11 @@
       <c r="AK94" s="3">
         <v>-100</v>
       </c>
+      <c r="AL94" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9054,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -9080,8 +9313,8 @@
       <c r="J96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -9161,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9268,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -9375,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -9482,20 +9724,23 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -9509,17 +9754,17 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -9536,13 +9781,13 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>6000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>500</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>91</v>
@@ -9550,14 +9795,14 @@
       <c r="X100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
+      <c r="Y100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
@@ -9566,11 +9811,11 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>100</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
@@ -9581,51 +9826,54 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>100</v>
       </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-100</v>
       </c>
       <c r="O101" s="3">
         <v>-100</v>
@@ -9637,23 +9885,23 @@
         <v>-100</v>
       </c>
       <c r="R101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
@@ -9676,131 +9924,137 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-100</v>
-      </c>
-      <c r="AJ101" s="3">
-        <v>100</v>
       </c>
       <c r="AK101" s="3">
         <v>100</v>
       </c>
+      <c r="AL101" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>27700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>20500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>FKWL</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E8" s="3">
         <v>17800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>44300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>66200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>62600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>37400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>11800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>14400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>12700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E9" s="3">
         <v>14600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>36800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>55000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>50900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>30500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>9600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>11500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>10400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E10" s="3">
         <v>3200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1600</v>
       </c>
       <c r="N10" s="3">
         <v>1600</v>
       </c>
       <c r="O10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P10" s="3">
         <v>1400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>7500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1500</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>1400</v>
       </c>
       <c r="AG10" s="3">
         <v>1400</v>
       </c>
       <c r="AH10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AI10" s="3">
         <v>2200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2900</v>
-      </c>
-      <c r="AK10" s="3">
-        <v>2300</v>
       </c>
       <c r="AL10" s="3">
         <v>2300</v>
       </c>
+      <c r="AM10" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,25 +1193,26 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>800</v>
+      </c>
+      <c r="E12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>800</v>
-      </c>
-      <c r="H12" s="3">
-        <v>900</v>
       </c>
       <c r="I12" s="3">
         <v>900</v>
@@ -1207,16 +1221,16 @@
         <v>900</v>
       </c>
       <c r="K12" s="3">
+        <v>900</v>
+      </c>
+      <c r="L12" s="3">
         <v>1100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1000</v>
       </c>
       <c r="M12" s="3">
         <v>1000</v>
       </c>
       <c r="N12" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="O12" s="3">
         <v>1100</v>
@@ -1225,10 +1239,10 @@
         <v>1100</v>
       </c>
       <c r="Q12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R12" s="3">
         <v>1000</v>
-      </c>
-      <c r="R12" s="3">
-        <v>1200</v>
       </c>
       <c r="S12" s="3">
         <v>1200</v>
@@ -1237,40 +1251,40 @@
         <v>1200</v>
       </c>
       <c r="U12" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="V12" s="3">
         <v>1000</v>
       </c>
       <c r="W12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X12" s="3">
         <v>800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>800</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>700</v>
       </c>
       <c r="AB12" s="3">
         <v>700</v>
       </c>
       <c r="AC12" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD12" s="3">
         <v>800</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>700</v>
       </c>
       <c r="AE12" s="3">
         <v>700</v>
       </c>
       <c r="AF12" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AG12" s="3">
         <v>900</v>
@@ -1285,13 +1299,16 @@
         <v>900</v>
       </c>
       <c r="AK12" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AL12" s="3">
         <v>800</v>
       </c>
+      <c r="AM12" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,22 +1417,25 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>91</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>91</v>
@@ -1423,41 +1443,41 @@
       <c r="I14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="3">
         <v>2400</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-200</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-500</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>91</v>
@@ -1474,8 +1494,8 @@
       <c r="Z14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1510,8 +1530,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1519,16 +1542,16 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
         <v>300</v>
       </c>
       <c r="G15" s="3">
+        <v>300</v>
+      </c>
+      <c r="H15" s="3">
         <v>200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -1537,11 +1560,11 @@
         <v>300</v>
       </c>
       <c r="K15" s="3">
+        <v>300</v>
+      </c>
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E17" s="3">
         <v>17000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>39100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>57000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>53400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>32600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>11800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>13700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>12300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1600</v>
       </c>
       <c r="H18" s="3">
         <v>-1600</v>
       </c>
       <c r="I18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5200</v>
-      </c>
-      <c r="T18" s="3">
-        <v>9200</v>
       </c>
       <c r="U18" s="3">
         <v>9200</v>
       </c>
       <c r="V18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="W18" s="3">
         <v>4800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-700</v>
       </c>
-      <c r="AH18" s="3">
-        <v>0</v>
-      </c>
       <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>700</v>
-      </c>
-      <c r="AK18" s="3">
-        <v>400</v>
       </c>
       <c r="AL18" s="3">
         <v>400</v>
       </c>
+      <c r="AM18" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1917,74 +1950,75 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>200</v>
       </c>
       <c r="G20" s="3">
         <v>200</v>
       </c>
       <c r="H20" s="3">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1998,19 +2032,19 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>100</v>
       </c>
       <c r="AH20" s="3">
         <v>100</v>
@@ -2022,123 +2056,129 @@
         <v>100</v>
       </c>
       <c r="AK20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5500</v>
-      </c>
-      <c r="T21" s="3">
-        <v>9300</v>
       </c>
       <c r="U21" s="3">
         <v>9300</v>
       </c>
       <c r="V21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="W21" s="3">
         <v>5000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-200</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>-400</v>
       </c>
       <c r="AG21" s="3">
         <v>-400</v>
       </c>
       <c r="AH21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AI21" s="3">
         <v>200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2166,8 +2206,8 @@
       <c r="K22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2247,228 +2287,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100</v>
       </c>
-      <c r="AI23" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3">
         <v>800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
-      </c>
-      <c r="X24" s="3">
-        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>100</v>
       </c>
       <c r="Z24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>-100</v>
       </c>
       <c r="AB24" s="3">
         <v>-100</v>
       </c>
       <c r="AC24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-100</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1100</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>4200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-400</v>
       </c>
-      <c r="AH26" s="3">
-        <v>0</v>
-      </c>
       <c r="AI26" s="3">
         <v>0</v>
       </c>
       <c r="AJ26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3">
         <v>500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1100</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>3900</v>
-      </c>
-      <c r="T27" s="3">
-        <v>6900</v>
       </c>
       <c r="U27" s="3">
         <v>6900</v>
       </c>
       <c r="V27" s="3">
+        <v>6900</v>
+      </c>
+      <c r="W27" s="3">
         <v>3700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>200</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-100</v>
       </c>
       <c r="AE27" s="3">
         <v>-100</v>
       </c>
       <c r="AF27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-400</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
       <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2957,8 +3018,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>91</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>91</v>
@@ -2978,11 +3039,11 @@
       <c r="Y29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>91</v>
@@ -2990,11 +3051,11 @@
       <c r="AC29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-700</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>91</v>
@@ -3005,8 +3066,8 @@
       <c r="AH29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
+      <c r="AI29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AJ29" s="3">
         <v>0</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3237,74 +3304,77 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-200</v>
       </c>
       <c r="G32" s="3">
         <v>-200</v>
       </c>
       <c r="H32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -3318,19 +3388,19 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>100</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-100</v>
       </c>
       <c r="AH32" s="3">
         <v>-100</v>
@@ -3342,123 +3412,129 @@
         <v>-100</v>
       </c>
       <c r="AK32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1100</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>3900</v>
-      </c>
-      <c r="T33" s="3">
-        <v>6900</v>
       </c>
       <c r="U33" s="3">
         <v>6900</v>
       </c>
       <c r="V33" s="3">
+        <v>6900</v>
+      </c>
+      <c r="W33" s="3">
         <v>3700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-400</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
       <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1100</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>3900</v>
-      </c>
-      <c r="T35" s="3">
-        <v>6900</v>
       </c>
       <c r="U35" s="3">
         <v>6900</v>
       </c>
       <c r="V35" s="3">
+        <v>6900</v>
+      </c>
+      <c r="W35" s="3">
         <v>3700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-400</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
       <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3872,159 +3958,163 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E41" s="3">
         <v>20300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>39300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>45800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>54400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>71000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>43300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>28200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>11700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>10900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E42" s="3">
         <v>21900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>24700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>26700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>16400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>16600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6600</v>
-      </c>
-      <c r="P42" s="3">
-        <v>5400</v>
       </c>
       <c r="Q42" s="3">
         <v>5400</v>
@@ -4056,8 +4146,8 @@
       <c r="Z42" s="3">
         <v>5400</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>91</v>
+      <c r="AA42" s="3">
+        <v>5400</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>91</v>
@@ -4071,8 +4161,8 @@
       <c r="AE42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AF42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
@@ -4092,236 +4182,245 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>16400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>16000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>11100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>13800</v>
-      </c>
-      <c r="AK43" s="3">
-        <v>12400</v>
       </c>
       <c r="AL43" s="3">
         <v>12400</v>
       </c>
+      <c r="AM43" s="3">
+        <v>12400</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E44" s="3">
         <v>4200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>11800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>800</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>1900</v>
       </c>
       <c r="AC44" s="3">
         <v>1900</v>
       </c>
       <c r="AD44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AE44" s="3">
         <v>1600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>200</v>
       </c>
       <c r="F45" s="3">
         <v>200</v>
@@ -4333,7 +4432,7 @@
         <v>200</v>
       </c>
       <c r="I45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J45" s="3">
         <v>100</v>
@@ -4342,25 +4441,25 @@
         <v>100</v>
       </c>
       <c r="L45" s="3">
+        <v>100</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>200</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
       </c>
       <c r="O45" s="3">
+        <v>200</v>
+      </c>
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>100</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
@@ -4372,7 +4471,7 @@
         <v>100</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -4384,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
         <v>100</v>
@@ -4399,19 +4498,19 @@
         <v>100</v>
       </c>
       <c r="AE45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF45" s="3">
         <v>200</v>
       </c>
       <c r="AG45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH45" s="3">
         <v>100</v>
       </c>
       <c r="AI45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AJ45" s="3">
         <v>500</v>
@@ -4420,120 +4519,126 @@
         <v>500</v>
       </c>
       <c r="AL45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AM45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E46" s="3">
         <v>48600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>45300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>40200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>47800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>46100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>51900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>47300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>50400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>47000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>48400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>53300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>45500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>47200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>54800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>74400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>106100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>79400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>61400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>25100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>25300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>20700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>19600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>21600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>27600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>21700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>19900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>21900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>21200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>28900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>23900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>28100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>25900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>27900</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -4561,8 +4666,8 @@
       <c r="K47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4642,79 +4747,82 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>300</v>
       </c>
       <c r="L48" s="3">
+        <v>300</v>
+      </c>
+      <c r="M48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>500</v>
-      </c>
-      <c r="N48" s="3">
-        <v>600</v>
       </c>
       <c r="O48" s="3">
         <v>600</v>
       </c>
       <c r="P48" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q48" s="3">
         <v>700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1500</v>
-      </c>
-      <c r="X48" s="3">
-        <v>1600</v>
       </c>
       <c r="Y48" s="3">
         <v>1600</v>
       </c>
       <c r="Z48" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="AA48" s="3">
         <v>100</v>
@@ -4732,7 +4840,7 @@
         <v>100</v>
       </c>
       <c r="AF48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG48" s="3">
         <v>200</v>
@@ -4744,7 +4852,7 @@
         <v>200</v>
       </c>
       <c r="AJ48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AK48" s="3">
         <v>300</v>
@@ -4752,8 +4860,11 @@
       <c r="AL48" s="3">
         <v>300</v>
       </c>
+      <c r="AM48" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
@@ -4761,109 +4872,112 @@
         <v>1100</v>
       </c>
       <c r="E49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F49" s="3">
         <v>1400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1900</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1600</v>
       </c>
       <c r="O49" s="3">
         <v>1600</v>
       </c>
       <c r="P49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q49" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1500</v>
       </c>
       <c r="R49" s="3">
         <v>1500</v>
       </c>
       <c r="S49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T49" s="3">
         <v>1600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1700</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1400</v>
       </c>
       <c r="V49" s="3">
         <v>1400</v>
       </c>
       <c r="W49" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="X49" s="3">
         <v>1500</v>
       </c>
       <c r="Y49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z49" s="3">
         <v>1700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>1100</v>
       </c>
       <c r="AB49" s="3">
         <v>1100</v>
       </c>
       <c r="AC49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD49" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>1300</v>
       </c>
       <c r="AE49" s="3">
         <v>1300</v>
       </c>
       <c r="AF49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AG49" s="3">
         <v>1400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1400</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>1300</v>
       </c>
       <c r="AJ49" s="3">
         <v>1300</v>
       </c>
       <c r="AK49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="AL49" s="3">
         <v>1400</v>
       </c>
+      <c r="AM49" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -5112,76 +5232,76 @@
         <v>100</v>
       </c>
       <c r="L52" s="3">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2100</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>2000</v>
       </c>
       <c r="AD52" s="3">
         <v>2000</v>
       </c>
       <c r="AE52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF52" s="3">
         <v>1900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1800</v>
-      </c>
-      <c r="AI52" s="3">
-        <v>1900</v>
       </c>
       <c r="AJ52" s="3">
         <v>1900</v>
@@ -5190,10 +5310,13 @@
         <v>1900</v>
       </c>
       <c r="AL52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AM52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E54" s="3">
         <v>54500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>51600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>46700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>50000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>52600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>50900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>56900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>52400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>54600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>51000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>50500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>57800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>78000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>109700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>83100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>65400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>30300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>30800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>26600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>24900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>30800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>25200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>24800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>32300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>27300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>31600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>29500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5492,118 +5622,122 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E57" s="3">
         <v>13800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>27900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>63900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>44900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>42100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>7600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>7000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>11800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>10600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -5611,28 +5745,28 @@
         <v>400</v>
       </c>
       <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
         <v>300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>200</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>100</v>
-      </c>
-      <c r="J58" s="3">
-        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5712,13 +5846,16 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
@@ -5727,79 +5864,79 @@
         <v>200</v>
       </c>
       <c r="G59" s="3">
+        <v>200</v>
+      </c>
+      <c r="H59" s="3">
         <v>2600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2700</v>
       </c>
       <c r="I59" s="3">
         <v>2700</v>
       </c>
       <c r="J59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1400</v>
       </c>
       <c r="R59" s="3">
         <v>1400</v>
       </c>
       <c r="S59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T59" s="3">
         <v>3500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>200</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>300</v>
       </c>
       <c r="AB59" s="3">
         <v>300</v>
       </c>
       <c r="AC59" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AD59" s="3">
         <v>500</v>
       </c>
       <c r="AE59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AF59" s="3">
         <v>300</v>
@@ -5811,137 +5948,143 @@
         <v>300</v>
       </c>
       <c r="AI59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E60" s="3">
         <v>16300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>31300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>67300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>47500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>43000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>13700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>13200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>12600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>11000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1200</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1300</v>
       </c>
       <c r="F61" s="3">
         <v>1300</v>
@@ -5950,7 +6093,7 @@
         <v>1300</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -6042,8 +6185,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
@@ -6071,50 +6217,50 @@
       <c r="K62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>100</v>
-      </c>
-      <c r="N62" s="3">
-        <v>200</v>
       </c>
       <c r="O62" s="3">
         <v>200</v>
       </c>
       <c r="P62" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q62" s="3">
         <v>300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>400</v>
-      </c>
-      <c r="R62" s="3">
-        <v>500</v>
       </c>
       <c r="S62" s="3">
         <v>500</v>
       </c>
       <c r="T62" s="3">
+        <v>500</v>
+      </c>
+      <c r="U62" s="3">
         <v>600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>91</v>
@@ -6131,8 +6277,8 @@
       <c r="AE62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AF62" s="3">
-        <v>0</v>
+      <c r="AF62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E66" s="3">
         <v>17500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>33300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>69100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>49700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>45000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7072,103 +7243,106 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E72" s="3">
         <v>25900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>26900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>30800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>32000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>32700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>33400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>34600</v>
-      </c>
-      <c r="R72" s="3">
-        <v>35700</v>
       </c>
       <c r="S72" s="3">
         <v>35700</v>
       </c>
       <c r="T72" s="3">
+        <v>35700</v>
+      </c>
+      <c r="U72" s="3">
         <v>31800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>24900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>14700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15400</v>
-      </c>
-      <c r="AH72" s="3">
-        <v>15800</v>
       </c>
       <c r="AI72" s="3">
         <v>15800</v>
@@ -7177,13 +7351,16 @@
         <v>15800</v>
       </c>
       <c r="AK72" s="3">
+        <v>15800</v>
+      </c>
+      <c r="AL72" s="3">
         <v>15200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E76" s="3">
         <v>36000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>36900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>38100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>38600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>38900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>40400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>39800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>42400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43600</v>
-      </c>
-      <c r="R76" s="3">
-        <v>44700</v>
       </c>
       <c r="S76" s="3">
         <v>44700</v>
       </c>
       <c r="T76" s="3">
+        <v>44700</v>
+      </c>
+      <c r="U76" s="3">
         <v>40700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>33400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>16300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>16100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>16900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17700</v>
-      </c>
-      <c r="AH76" s="3">
-        <v>18100</v>
       </c>
       <c r="AI76" s="3">
         <v>18100</v>
       </c>
       <c r="AJ76" s="3">
+        <v>18100</v>
+      </c>
+      <c r="AK76" s="3">
         <v>18000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1100</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>3900</v>
-      </c>
-      <c r="T81" s="3">
-        <v>6900</v>
       </c>
       <c r="U81" s="3">
         <v>6900</v>
       </c>
       <c r="V81" s="3">
+        <v>6900</v>
+      </c>
+      <c r="W81" s="3">
         <v>3700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-400</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
       <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -8027,7 +8226,7 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
@@ -8042,7 +8241,7 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -8054,7 +8253,7 @@
         <v>100</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
@@ -8063,7 +8262,7 @@
         <v>200</v>
       </c>
       <c r="X83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
@@ -8075,7 +8274,7 @@
         <v>100</v>
       </c>
       <c r="AB83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>200</v>
@@ -8084,22 +8283,22 @@
         <v>200</v>
       </c>
       <c r="AE83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF83" s="3">
         <v>100</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>200</v>
       </c>
       <c r="AG83" s="3">
         <v>200</v>
       </c>
       <c r="AH83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AI83" s="3">
         <v>100</v>
       </c>
       <c r="AJ83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AK83" s="3">
         <v>200</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>200</v>
       </c>
+      <c r="AM83" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>2700</v>
+        <v>-5900</v>
       </c>
       <c r="E89" s="3">
         <v>2700</v>
       </c>
       <c r="F89" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G89" s="3">
         <v>6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-16600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>27900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>20100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4900</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
@@ -8837,23 +9058,23 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -8873,23 +9094,23 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="3">
         <v>-100</v>
       </c>
       <c r="Z91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
@@ -8906,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="AI91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ91" s="3">
         <v>-100</v>
@@ -8917,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>-100</v>
       </c>
+      <c r="AM91" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -9137,106 +9364,109 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E94" s="3">
         <v>3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
       </c>
       <c r="T94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U94" s="3">
         <v>-500</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-100</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
       </c>
       <c r="W94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AI94" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ94" s="3">
         <v>-100</v>
@@ -9247,8 +9477,11 @@
       <c r="AL94" s="3">
         <v>-100</v>
       </c>
+      <c r="AM94" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -9316,8 +9550,8 @@
       <c r="K96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -9727,8 +9970,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
@@ -9738,12 +9984,12 @@
       <c r="E100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -9757,17 +10003,17 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -9784,13 +10030,13 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>6000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>500</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>91</v>
@@ -9798,14 +10044,14 @@
       <c r="Y100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
+      <c r="Z100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
@@ -9814,11 +10060,11 @@
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
@@ -9829,54 +10075,57 @@
         <v>0</v>
       </c>
       <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>100</v>
       </c>
-      <c r="AK100" s="3">
-        <v>0</v>
-      </c>
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-100</v>
       </c>
       <c r="P101" s="3">
         <v>-100</v>
@@ -9888,23 +10137,23 @@
         <v>-100</v>
       </c>
       <c r="S101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
@@ -9927,134 +10176,140 @@
         <v>0</v>
       </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
         <v>0</v>
       </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-100</v>
-      </c>
-      <c r="AK101" s="3">
-        <v>100</v>
       </c>
       <c r="AL101" s="3">
         <v>100</v>
       </c>
+      <c r="AM101" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E102" s="3">
         <v>5600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>27700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>20500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
@@ -5855,7 +5855,7 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>

--- a/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>FKWL</t>
   </si>
@@ -656,531 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E8" s="3">
         <v>12700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>44300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>66200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>62600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>37400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>15500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>11800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>14400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>12700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E9" s="3">
         <v>9800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>36800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>55000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>50900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>30500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>10700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>11200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>6200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>9600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>7800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>11500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>10400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1000</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1600</v>
       </c>
       <c r="Q10" s="3">
         <v>1600</v>
       </c>
       <c r="R10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S10" s="3">
         <v>1400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1500</v>
-      </c>
-      <c r="AI10" s="3">
-        <v>1400</v>
       </c>
       <c r="AJ10" s="3">
         <v>1400</v>
       </c>
       <c r="AK10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AL10" s="3">
         <v>2200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2900</v>
-      </c>
-      <c r="AN10" s="3">
-        <v>2300</v>
       </c>
       <c r="AO10" s="3">
         <v>2300</v>
       </c>
+      <c r="AP10" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1222,34 +1234,35 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>800</v>
+      </c>
+      <c r="E12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>800</v>
-      </c>
-      <c r="K12" s="3">
-        <v>900</v>
       </c>
       <c r="L12" s="3">
         <v>900</v>
@@ -1258,16 +1271,16 @@
         <v>900</v>
       </c>
       <c r="N12" s="3">
+        <v>900</v>
+      </c>
+      <c r="O12" s="3">
         <v>1100</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1000</v>
       </c>
       <c r="P12" s="3">
         <v>1000</v>
       </c>
       <c r="Q12" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="R12" s="3">
         <v>1100</v>
@@ -1276,10 +1289,10 @@
         <v>1100</v>
       </c>
       <c r="T12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U12" s="3">
         <v>1000</v>
-      </c>
-      <c r="U12" s="3">
-        <v>1200</v>
       </c>
       <c r="V12" s="3">
         <v>1200</v>
@@ -1288,40 +1301,40 @@
         <v>1200</v>
       </c>
       <c r="X12" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="Y12" s="3">
         <v>1000</v>
       </c>
       <c r="Z12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA12" s="3">
         <v>800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>800</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>700</v>
       </c>
       <c r="AE12" s="3">
         <v>700</v>
       </c>
       <c r="AF12" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG12" s="3">
         <v>800</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>700</v>
       </c>
       <c r="AH12" s="3">
         <v>700</v>
       </c>
       <c r="AI12" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AJ12" s="3">
         <v>900</v>
@@ -1336,13 +1349,16 @@
         <v>900</v>
       </c>
       <c r="AN12" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AO12" s="3">
         <v>800</v>
       </c>
+      <c r="AP12" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1460,31 +1476,34 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1000</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>91</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>91</v>
@@ -1492,41 +1511,41 @@
       <c r="L14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N14" s="3">
         <v>2400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-500</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>91</v>
@@ -1543,8 +1562,8 @@
       <c r="AC14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1579,8 +1598,11 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1597,16 +1619,16 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
       </c>
       <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3">
         <v>200</v>
-      </c>
-      <c r="K15" s="3">
-        <v>300</v>
       </c>
       <c r="L15" s="3">
         <v>300</v>
@@ -1615,11 +1637,11 @@
         <v>300</v>
       </c>
       <c r="N15" s="3">
+        <v>300</v>
+      </c>
+      <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1698,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E17" s="3">
         <v>12200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>39100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>57000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>53400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>32600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>11800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>13700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>12300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
         <v>600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1600</v>
       </c>
       <c r="K18" s="3">
         <v>-1600</v>
       </c>
       <c r="L18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5200</v>
-      </c>
-      <c r="W18" s="3">
-        <v>9200</v>
       </c>
       <c r="X18" s="3">
         <v>9200</v>
       </c>
       <c r="Y18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Z18" s="3">
         <v>4800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-700</v>
       </c>
-      <c r="AK18" s="3">
-        <v>0</v>
-      </c>
       <c r="AL18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="3">
         <v>-100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>700</v>
-      </c>
-      <c r="AN18" s="3">
-        <v>400</v>
       </c>
       <c r="AO18" s="3">
         <v>400</v>
       </c>
+      <c r="AP18" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2019,83 +2051,84 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>200</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
       </c>
       <c r="K20" s="3">
+        <v>200</v>
+      </c>
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -2109,19 +2142,19 @@
         <v>0</v>
       </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>100</v>
       </c>
       <c r="AK20" s="3">
         <v>100</v>
@@ -2133,132 +2166,138 @@
         <v>100</v>
       </c>
       <c r="AN20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>200</v>
+      </c>
+      <c r="E21" s="3">
         <v>600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5500</v>
-      </c>
-      <c r="W21" s="3">
-        <v>9300</v>
       </c>
       <c r="X21" s="3">
         <v>9300</v>
       </c>
       <c r="Y21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="Z21" s="3">
         <v>5000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-200</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>-400</v>
       </c>
       <c r="AJ21" s="3">
         <v>-400</v>
       </c>
       <c r="AK21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AL21" s="3">
         <v>200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2295,8 +2334,8 @@
       <c r="N22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2376,127 +2415,133 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>500</v>
+      </c>
+      <c r="E23" s="3">
         <v>600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>9100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>100</v>
       </c>
-      <c r="AL23" s="3">
-        <v>0</v>
-      </c>
       <c r="AM23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="3">
         <v>800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2504,118 +2549,121 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>100</v>
       </c>
       <c r="AB24" s="3">
         <v>100</v>
       </c>
       <c r="AC24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>-100</v>
       </c>
       <c r="AE24" s="3">
         <v>-100</v>
       </c>
       <c r="AF24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-100</v>
       </c>
-      <c r="AK24" s="3">
-        <v>0</v>
-      </c>
       <c r="AL24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="3">
         <v>-100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2733,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>500</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1100</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>4200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-400</v>
       </c>
-      <c r="AK26" s="3">
-        <v>0</v>
-      </c>
       <c r="AL26" s="3">
         <v>0</v>
       </c>
       <c r="AM26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="3">
         <v>500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>500</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1100</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>3900</v>
-      </c>
-      <c r="W27" s="3">
-        <v>6900</v>
       </c>
       <c r="X27" s="3">
         <v>6900</v>
       </c>
       <c r="Y27" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Z27" s="3">
         <v>3700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>200</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>-100</v>
       </c>
       <c r="AH27" s="3">
         <v>-100</v>
       </c>
       <c r="AI27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-400</v>
       </c>
-      <c r="AK27" s="3">
-        <v>0</v>
-      </c>
       <c r="AL27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="3">
         <v>100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3090,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3149,8 +3209,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>91</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>91</v>
@@ -3170,11 +3230,11 @@
       <c r="AB29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>91</v>
@@ -3182,11 +3242,11 @@
       <c r="AF29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-700</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>91</v>
@@ -3197,8 +3257,8 @@
       <c r="AK29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
+      <c r="AL29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AM29" s="3">
         <v>0</v>
@@ -3209,8 +3269,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3328,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3447,83 +3513,86 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-200</v>
       </c>
       <c r="J32" s="3">
         <v>-200</v>
       </c>
       <c r="K32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -3537,19 +3606,19 @@
         <v>0</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>100</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>-100</v>
       </c>
       <c r="AK32" s="3">
         <v>-100</v>
@@ -3561,132 +3630,138 @@
         <v>-100</v>
       </c>
       <c r="AN32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>500</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1100</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>3900</v>
-      </c>
-      <c r="W33" s="3">
-        <v>6900</v>
       </c>
       <c r="X33" s="3">
         <v>6900</v>
       </c>
       <c r="Y33" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Z33" s="3">
         <v>3700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-400</v>
       </c>
-      <c r="AK33" s="3">
-        <v>0</v>
-      </c>
       <c r="AL33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="3">
         <v>100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3804,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>500</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1100</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>3900</v>
-      </c>
-      <c r="W35" s="3">
-        <v>6900</v>
       </c>
       <c r="X35" s="3">
         <v>6900</v>
       </c>
       <c r="Y35" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Z35" s="3">
         <v>3700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-400</v>
       </c>
-      <c r="AK35" s="3">
-        <v>0</v>
-      </c>
       <c r="AL35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="3">
         <v>100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4090,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4133,177 +4218,181 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E41" s="3">
         <v>13400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>26300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>36500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>45800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>54400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>71000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>28200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>16800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>12000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>12100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>13500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>11800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>14300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>12500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>11700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>10900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E42" s="3">
         <v>25300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>21900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>25200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>24700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>27500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>26700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>16600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>15300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>16300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>6600</v>
-      </c>
-      <c r="S42" s="3">
-        <v>5400</v>
       </c>
       <c r="T42" s="3">
         <v>5400</v>
@@ -4335,8 +4424,8 @@
       <c r="AC42" s="3">
         <v>5400</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>91</v>
+      <c r="AD42" s="3">
+        <v>5400</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>91</v>
@@ -4350,8 +4439,8 @@
       <c r="AH42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AI42" s="3">
-        <v>0</v>
+      <c r="AI42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AJ42" s="3">
         <v>0</v>
@@ -4371,263 +4460,272 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>16400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>27900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>16000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>11300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>11100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>9600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>13800</v>
-      </c>
-      <c r="AN43" s="3">
-        <v>12400</v>
       </c>
       <c r="AO43" s="3">
         <v>12400</v>
       </c>
+      <c r="AP43" s="3">
+        <v>12400</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>13200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>11800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>800</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>1900</v>
       </c>
       <c r="AF44" s="3">
         <v>1900</v>
       </c>
       <c r="AG44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AH44" s="3">
         <v>1600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
         <v>200</v>
       </c>
       <c r="F45" s="3">
+        <v>200</v>
+      </c>
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
       </c>
       <c r="I45" s="3">
         <v>200</v>
@@ -4639,7 +4737,7 @@
         <v>200</v>
       </c>
       <c r="L45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M45" s="3">
         <v>100</v>
@@ -4648,25 +4746,25 @@
         <v>100</v>
       </c>
       <c r="O45" s="3">
+        <v>100</v>
+      </c>
+      <c r="P45" s="3">
         <v>300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
       </c>
       <c r="R45" s="3">
+        <v>200</v>
+      </c>
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
-      </c>
-      <c r="U45" s="3">
-        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
@@ -4678,7 +4776,7 @@
         <v>100</v>
       </c>
       <c r="Y45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
@@ -4690,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="AC45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="3">
         <v>100</v>
@@ -4705,19 +4803,19 @@
         <v>100</v>
       </c>
       <c r="AH45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AI45" s="3">
         <v>200</v>
       </c>
       <c r="AJ45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AK45" s="3">
         <v>100</v>
       </c>
       <c r="AL45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM45" s="3">
         <v>500</v>
@@ -4726,129 +4824,135 @@
         <v>500</v>
       </c>
       <c r="AO45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AP45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E46" s="3">
         <v>47400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>45200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>48600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>45300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>40200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>43500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>47800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>46100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>51900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>47300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>50400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>47000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>48400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>53300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>45500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>47200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>54800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>74400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>106100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>79400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>61400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>25100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>25300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>20700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>19600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>21600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>27600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>21700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>19900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>21200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>28900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>23900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>28100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>25900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>27900</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -4885,8 +4989,8 @@
       <c r="N47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4966,8 +5070,11 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
@@ -4975,79 +5082,79 @@
         <v>1300</v>
       </c>
       <c r="E48" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="F48" s="3">
         <v>1500</v>
       </c>
       <c r="G48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H48" s="3">
         <v>1600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>200</v>
-      </c>
-      <c r="M48" s="3">
-        <v>300</v>
       </c>
       <c r="N48" s="3">
         <v>300</v>
       </c>
       <c r="O48" s="3">
+        <v>300</v>
+      </c>
+      <c r="P48" s="3">
         <v>400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>500</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>600</v>
       </c>
       <c r="R48" s="3">
         <v>600</v>
       </c>
       <c r="S48" s="3">
+        <v>600</v>
+      </c>
+      <c r="T48" s="3">
         <v>700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1500</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>1600</v>
       </c>
       <c r="AB48" s="3">
         <v>1600</v>
       </c>
       <c r="AC48" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="AD48" s="3">
         <v>100</v>
@@ -5065,7 +5172,7 @@
         <v>100</v>
       </c>
       <c r="AI48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AJ48" s="3">
         <v>200</v>
@@ -5077,7 +5184,7 @@
         <v>200</v>
       </c>
       <c r="AM48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AN48" s="3">
         <v>300</v>
@@ -5085,127 +5192,133 @@
       <c r="AO48" s="3">
         <v>300</v>
       </c>
+      <c r="AP48" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1300</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1100</v>
       </c>
       <c r="G49" s="3">
         <v>1100</v>
       </c>
       <c r="H49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I49" s="3">
         <v>1400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1600</v>
       </c>
       <c r="R49" s="3">
         <v>1600</v>
       </c>
       <c r="S49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T49" s="3">
         <v>1700</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1500</v>
       </c>
       <c r="U49" s="3">
         <v>1500</v>
       </c>
       <c r="V49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W49" s="3">
         <v>1600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1700</v>
-      </c>
-      <c r="X49" s="3">
-        <v>1400</v>
       </c>
       <c r="Y49" s="3">
         <v>1400</v>
       </c>
       <c r="Z49" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="AA49" s="3">
         <v>1500</v>
       </c>
       <c r="AB49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AC49" s="3">
         <v>1700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>1100</v>
       </c>
       <c r="AE49" s="3">
         <v>1100</v>
       </c>
       <c r="AF49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG49" s="3">
         <v>1200</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>1300</v>
       </c>
       <c r="AH49" s="3">
         <v>1300</v>
       </c>
       <c r="AI49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1400</v>
-      </c>
-      <c r="AL49" s="3">
-        <v>1300</v>
       </c>
       <c r="AM49" s="3">
         <v>1300</v>
       </c>
       <c r="AN49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="AO49" s="3">
         <v>1400</v>
       </c>
+      <c r="AP49" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5323,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5442,8 +5558,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -5481,76 +5600,76 @@
         <v>100</v>
       </c>
       <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
         <v>1500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2100</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>2000</v>
       </c>
       <c r="AG52" s="3">
         <v>2000</v>
       </c>
       <c r="AH52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AI52" s="3">
         <v>1900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1800</v>
-      </c>
-      <c r="AL52" s="3">
-        <v>1900</v>
       </c>
       <c r="AM52" s="3">
         <v>1900</v>
@@ -5559,10 +5678,13 @@
         <v>1900</v>
       </c>
       <c r="AO52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AP52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5680,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E54" s="3">
         <v>53300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>51300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>49700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>54500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>51600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>46700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>50000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>52600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>50900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>56900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>54600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>51000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>52000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>57200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>49400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>50500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>57800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>78000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>109700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>83100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>65400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>30300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>26600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>23100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>24900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>30800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>25100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>25200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>24800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>32300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>27300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>31600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>29500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5842,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5885,127 +6014,131 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E57" s="3">
         <v>9600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>27900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>63900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>44900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>42100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>7600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>5800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>12900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>7200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>11800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>10600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -6022,28 +6155,28 @@
         <v>400</v>
       </c>
       <c r="H58" s="3">
+        <v>400</v>
+      </c>
+      <c r="I58" s="3">
         <v>300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>200</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>100</v>
-      </c>
-      <c r="M58" s="3">
-        <v>200</v>
       </c>
       <c r="N58" s="3">
         <v>200</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -6123,8 +6256,11 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
@@ -6147,79 +6283,79 @@
         <v>200</v>
       </c>
       <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
         <v>2600</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2700</v>
       </c>
       <c r="L59" s="3">
         <v>2700</v>
       </c>
       <c r="M59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N59" s="3">
         <v>2600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1600</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1400</v>
       </c>
       <c r="U59" s="3">
         <v>1400</v>
       </c>
       <c r="V59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W59" s="3">
         <v>3500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>200</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>300</v>
       </c>
       <c r="AE59" s="3">
         <v>300</v>
       </c>
       <c r="AF59" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AG59" s="3">
         <v>500</v>
       </c>
       <c r="AH59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AI59" s="3">
         <v>300</v>
@@ -6231,155 +6367,161 @@
         <v>300</v>
       </c>
       <c r="AL59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AM59" s="3">
         <v>1000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E60" s="3">
         <v>14000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>31300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>67300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>47500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>43000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>13500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>13200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>8200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>12600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>11000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>800</v>
+      </c>
+      <c r="E61" s="3">
         <v>900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1200</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1300</v>
       </c>
       <c r="I61" s="3">
         <v>1300</v>
@@ -6388,7 +6530,7 @@
         <v>1300</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -6480,8 +6622,11 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
@@ -6518,50 +6663,50 @@
       <c r="N62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>100</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>200</v>
       </c>
       <c r="R62" s="3">
         <v>200</v>
       </c>
       <c r="S62" s="3">
+        <v>200</v>
+      </c>
+      <c r="T62" s="3">
         <v>300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>400</v>
-      </c>
-      <c r="U62" s="3">
-        <v>500</v>
       </c>
       <c r="V62" s="3">
         <v>500</v>
       </c>
       <c r="W62" s="3">
+        <v>500</v>
+      </c>
+      <c r="X62" s="3">
         <v>600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>91</v>
@@ -6578,8 +6723,8 @@
       <c r="AH62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AI62" s="3">
-        <v>0</v>
+      <c r="AI62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AJ62" s="3">
         <v>0</v>
@@ -6599,8 +6744,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6718,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6837,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -6956,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E66" s="3">
         <v>14900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>69100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>49700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>45000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>14500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>14200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>9200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>13600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>12000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7118,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7237,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7356,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7475,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7594,112 +7764,115 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E72" s="3">
         <v>25500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>28800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>29100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>30700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>30500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>30800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>32000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>32700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>33400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>34600</v>
-      </c>
-      <c r="U72" s="3">
-        <v>35700</v>
       </c>
       <c r="V72" s="3">
         <v>35700</v>
       </c>
       <c r="W72" s="3">
+        <v>35700</v>
+      </c>
+      <c r="X72" s="3">
         <v>31800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>24900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>14500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>14700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15400</v>
-      </c>
-      <c r="AK72" s="3">
-        <v>15800</v>
       </c>
       <c r="AL72" s="3">
         <v>15800</v>
@@ -7708,13 +7881,16 @@
         <v>15800</v>
       </c>
       <c r="AN72" s="3">
+        <v>15800</v>
+      </c>
+      <c r="AO72" s="3">
         <v>15200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7832,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -7951,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8070,8 +8252,11 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
@@ -8079,118 +8264,121 @@
         <v>35100</v>
       </c>
       <c r="E76" s="3">
+        <v>35100</v>
+      </c>
+      <c r="F76" s="3">
         <v>34500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>36000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>36900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>38100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>38600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>38900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>40400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>40100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>39800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>41000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>41700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>42400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>43600</v>
-      </c>
-      <c r="U76" s="3">
-        <v>44700</v>
       </c>
       <c r="V76" s="3">
         <v>44700</v>
       </c>
       <c r="W76" s="3">
+        <v>44700</v>
+      </c>
+      <c r="X76" s="3">
         <v>40700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>33400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>16300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>16100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>16900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>17000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>17700</v>
-      </c>
-      <c r="AK76" s="3">
-        <v>18100</v>
       </c>
       <c r="AL76" s="3">
         <v>18100</v>
       </c>
       <c r="AM76" s="3">
+        <v>18100</v>
+      </c>
+      <c r="AN76" s="3">
         <v>18000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>17500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8308,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>500</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1100</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>3900</v>
-      </c>
-      <c r="W81" s="3">
-        <v>6900</v>
       </c>
       <c r="X81" s="3">
         <v>6900</v>
       </c>
       <c r="Y81" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Z81" s="3">
         <v>3700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-400</v>
       </c>
-      <c r="AK81" s="3">
-        <v>0</v>
-      </c>
       <c r="AL81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="3">
         <v>100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8594,8 +8791,9 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -8606,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -8633,7 +8831,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
@@ -8648,7 +8846,7 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -8660,7 +8858,7 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
@@ -8669,7 +8867,7 @@
         <v>200</v>
       </c>
       <c r="AA83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB83" s="3">
         <v>100</v>
@@ -8681,7 +8879,7 @@
         <v>100</v>
       </c>
       <c r="AE83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF83" s="3">
         <v>200</v>
@@ -8690,22 +8888,22 @@
         <v>200</v>
       </c>
       <c r="AH83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI83" s="3">
         <v>100</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>200</v>
       </c>
       <c r="AJ83" s="3">
         <v>200</v>
       </c>
       <c r="AK83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AL83" s="3">
         <v>100</v>
       </c>
       <c r="AM83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AN83" s="3">
         <v>200</v>
@@ -8713,8 +8911,11 @@
       <c r="AO83" s="3">
         <v>200</v>
       </c>
+      <c r="AP83" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -8832,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -8951,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9070,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9189,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9308,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5900</v>
-      </c>
-      <c r="G89" s="3">
-        <v>2700</v>
       </c>
       <c r="H89" s="3">
         <v>2700</v>
       </c>
       <c r="I89" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J89" s="3">
         <v>6200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-16600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>27900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>20100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4900</v>
       </c>
-      <c r="AG89" s="3">
-        <v>0</v>
-      </c>
       <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9470,8 +9689,9 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
@@ -9509,23 +9729,23 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -9545,23 +9765,23 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB91" s="3">
         <v>-100</v>
       </c>
       <c r="AC91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
@@ -9578,7 +9798,7 @@
         <v>0</v>
       </c>
       <c r="AL91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AM91" s="3">
         <v>-100</v>
@@ -9589,8 +9809,11 @@
       <c r="AO91" s="3">
         <v>-100</v>
       </c>
+      <c r="AP91" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9708,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -9827,115 +10053,118 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>600</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
       </c>
       <c r="W94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X94" s="3">
         <v>-500</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-100</v>
       </c>
       <c r="Y94" s="3">
         <v>-100</v>
       </c>
       <c r="Z94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-300</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
-      <c r="AI94" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AL94" s="3">
-        <v>-100</v>
       </c>
       <c r="AM94" s="3">
         <v>-100</v>
@@ -9946,8 +10175,11 @@
       <c r="AO94" s="3">
         <v>-100</v>
       </c>
+      <c r="AP94" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -9989,13 +10221,14 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>91</v>
+      <c r="D96" s="3">
+        <v>500</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>91</v>
@@ -10027,8 +10260,8 @@
       <c r="N96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -10108,8 +10341,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10227,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10346,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10465,19 +10707,22 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>91</v>
@@ -10485,12 +10730,12 @@
       <c r="H100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -10504,17 +10749,17 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -10531,13 +10776,13 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>6000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>500</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>91</v>
@@ -10545,14 +10790,14 @@
       <c r="AB100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3" t="s">
+      <c r="AC100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
@@ -10561,11 +10806,11 @@
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>100</v>
       </c>
-      <c r="AI100" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
@@ -10576,63 +10821,66 @@
         <v>0</v>
       </c>
       <c r="AM100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="3">
         <v>100</v>
       </c>
-      <c r="AN100" s="3">
-        <v>0</v>
-      </c>
       <c r="AO100" s="3">
         <v>0</v>
       </c>
+      <c r="AP100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-100</v>
       </c>
       <c r="S101" s="3">
         <v>-100</v>
@@ -10644,23 +10892,23 @@
         <v>-100</v>
       </c>
       <c r="V101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
@@ -10683,143 +10931,149 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>100</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
         <v>0</v>
       </c>
       <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
         <v>100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-100</v>
-      </c>
-      <c r="AN101" s="3">
-        <v>100</v>
       </c>
       <c r="AO101" s="3">
         <v>100</v>
       </c>
+      <c r="AP101" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>27700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>15200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>20500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FKWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>FKWL</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E8" s="3">
         <v>11900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>44300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>66200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>62600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>37400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>15500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>11800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>14400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>12700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E9" s="3">
         <v>9900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>36800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>55000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>50900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>30500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>10700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>9600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>7800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>11500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>10400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1600</v>
       </c>
       <c r="R10" s="3">
         <v>1600</v>
       </c>
       <c r="S10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T10" s="3">
         <v>1400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>11700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1500</v>
-      </c>
-      <c r="AJ10" s="3">
-        <v>1400</v>
       </c>
       <c r="AK10" s="3">
         <v>1400</v>
       </c>
       <c r="AL10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AM10" s="3">
         <v>2200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2900</v>
-      </c>
-      <c r="AO10" s="3">
-        <v>2300</v>
       </c>
       <c r="AP10" s="3">
         <v>2300</v>
       </c>
+      <c r="AQ10" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1244,28 +1258,28 @@
         <v>800</v>
       </c>
       <c r="E12" s="3">
+        <v>800</v>
+      </c>
+      <c r="F12" s="3">
         <v>900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>800</v>
-      </c>
-      <c r="L12" s="3">
-        <v>900</v>
       </c>
       <c r="M12" s="3">
         <v>900</v>
@@ -1274,16 +1288,16 @@
         <v>900</v>
       </c>
       <c r="O12" s="3">
+        <v>900</v>
+      </c>
+      <c r="P12" s="3">
         <v>1100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1000</v>
       </c>
       <c r="Q12" s="3">
         <v>1000</v>
       </c>
       <c r="R12" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="S12" s="3">
         <v>1100</v>
@@ -1292,10 +1306,10 @@
         <v>1100</v>
       </c>
       <c r="U12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V12" s="3">
         <v>1000</v>
-      </c>
-      <c r="V12" s="3">
-        <v>1200</v>
       </c>
       <c r="W12" s="3">
         <v>1200</v>
@@ -1304,40 +1318,40 @@
         <v>1200</v>
       </c>
       <c r="Y12" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="Z12" s="3">
         <v>1000</v>
       </c>
       <c r="AA12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB12" s="3">
         <v>800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>800</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>700</v>
       </c>
       <c r="AF12" s="3">
         <v>700</v>
       </c>
       <c r="AG12" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH12" s="3">
         <v>800</v>
-      </c>
-      <c r="AH12" s="3">
-        <v>700</v>
       </c>
       <c r="AI12" s="3">
         <v>700</v>
       </c>
       <c r="AJ12" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AK12" s="3">
         <v>900</v>
@@ -1352,13 +1366,16 @@
         <v>900</v>
       </c>
       <c r="AO12" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AP12" s="3">
         <v>800</v>
       </c>
+      <c r="AQ12" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,34 +1496,37 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="3">
         <v>-400</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-1000</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>91</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>91</v>
@@ -1514,41 +1534,41 @@
       <c r="M14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O14" s="3">
         <v>2400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-500</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>91</v>
@@ -1565,8 +1585,8 @@
       <c r="AD14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1601,13 +1621,16 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1622,16 +1645,16 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
       </c>
       <c r="K15" s="3">
+        <v>300</v>
+      </c>
+      <c r="L15" s="3">
         <v>200</v>
-      </c>
-      <c r="L15" s="3">
-        <v>300</v>
       </c>
       <c r="M15" s="3">
         <v>300</v>
@@ -1640,11 +1663,11 @@
         <v>300</v>
       </c>
       <c r="O15" s="3">
+        <v>300</v>
+      </c>
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E17" s="3">
         <v>11900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>39100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>57000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>53400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>32600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>12500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>11800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>9800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>13700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>12300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
         <v>600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2200</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1600</v>
       </c>
       <c r="L18" s="3">
         <v>-1600</v>
       </c>
       <c r="M18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5200</v>
-      </c>
-      <c r="X18" s="3">
-        <v>9200</v>
       </c>
       <c r="Y18" s="3">
         <v>9200</v>
       </c>
       <c r="Z18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AA18" s="3">
         <v>4800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-700</v>
       </c>
-      <c r="AL18" s="3">
-        <v>0</v>
-      </c>
       <c r="AM18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="3">
         <v>-100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>700</v>
-      </c>
-      <c r="AO18" s="3">
-        <v>400</v>
       </c>
       <c r="AP18" s="3">
         <v>400</v>
       </c>
+      <c r="AQ18" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,86 +2085,87 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
       </c>
       <c r="L20" s="3">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>200</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -2145,19 +2179,19 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>200</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>100</v>
       </c>
       <c r="AL20" s="3">
         <v>100</v>
@@ -2169,135 +2203,141 @@
         <v>100</v>
       </c>
       <c r="AO20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5500</v>
-      </c>
-      <c r="X21" s="3">
-        <v>9300</v>
       </c>
       <c r="Y21" s="3">
         <v>9300</v>
       </c>
       <c r="Z21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AA21" s="3">
         <v>5000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-200</v>
-      </c>
-      <c r="AJ21" s="3">
-        <v>-400</v>
       </c>
       <c r="AK21" s="3">
         <v>-400</v>
       </c>
       <c r="AL21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AM21" s="3">
         <v>200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>500</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2337,8 +2377,8 @@
       <c r="O22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2418,130 +2458,136 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-400</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-1500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>100</v>
       </c>
-      <c r="AM23" s="3">
-        <v>0</v>
-      </c>
       <c r="AN23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="3">
         <v>800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2552,118 +2598,121 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>100</v>
       </c>
       <c r="AC24" s="3">
         <v>100</v>
       </c>
       <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-300</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>-100</v>
       </c>
       <c r="AF24" s="3">
         <v>-100</v>
       </c>
       <c r="AG24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-100</v>
       </c>
-      <c r="AL24" s="3">
-        <v>0</v>
-      </c>
       <c r="AM24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3">
         <v>-100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>4200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-400</v>
       </c>
-      <c r="AL26" s="3">
-        <v>0</v>
-      </c>
       <c r="AM26" s="3">
         <v>0</v>
       </c>
       <c r="AN26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="3">
         <v>500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>200</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>3900</v>
-      </c>
-      <c r="X27" s="3">
-        <v>6900</v>
       </c>
       <c r="Y27" s="3">
         <v>6900</v>
       </c>
       <c r="Z27" s="3">
+        <v>6900</v>
+      </c>
+      <c r="AA27" s="3">
         <v>3700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>200</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>-100</v>
       </c>
       <c r="AI27" s="3">
         <v>-100</v>
       </c>
       <c r="AJ27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-400</v>
       </c>
-      <c r="AL27" s="3">
-        <v>0</v>
-      </c>
       <c r="AM27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="3">
         <v>100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3212,8 +3273,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>91</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>91</v>
@@ -3233,11 +3294,11 @@
       <c r="AC29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>91</v>
@@ -3245,11 +3306,11 @@
       <c r="AG29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-700</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>91</v>
@@ -3260,8 +3321,8 @@
       <c r="AL29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AM29" s="3">
-        <v>0</v>
+      <c r="AM29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AN29" s="3">
         <v>0</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3516,86 +3583,89 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
       </c>
       <c r="L32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>-200</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3609,19 +3679,19 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-200</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>100</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>-100</v>
       </c>
       <c r="AL32" s="3">
         <v>-100</v>
@@ -3633,135 +3703,141 @@
         <v>-100</v>
       </c>
       <c r="AO32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>3900</v>
-      </c>
-      <c r="X33" s="3">
-        <v>6900</v>
       </c>
       <c r="Y33" s="3">
         <v>6900</v>
       </c>
       <c r="Z33" s="3">
+        <v>6900</v>
+      </c>
+      <c r="AA33" s="3">
         <v>3700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-400</v>
       </c>
-      <c r="AL33" s="3">
-        <v>0</v>
-      </c>
       <c r="AM33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="3">
         <v>100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>3900</v>
-      </c>
-      <c r="X35" s="3">
-        <v>6900</v>
       </c>
       <c r="Y35" s="3">
         <v>6900</v>
       </c>
       <c r="Z35" s="3">
+        <v>6900</v>
+      </c>
+      <c r="AA35" s="3">
         <v>3700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-400</v>
       </c>
-      <c r="AL35" s="3">
-        <v>0</v>
-      </c>
       <c r="AM35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="3">
         <v>100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4219,183 +4305,187 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E41" s="3">
         <v>9400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>25500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>26300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>36700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>39300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>45800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>54400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>71000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>28200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>16800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>12000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>13500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>11800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>14300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>12500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>11700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>10900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>13200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E42" s="3">
         <v>24300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>25300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>21900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>25200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>24700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>27500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>26800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>26700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>16400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>16600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>15300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>16300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>6600</v>
-      </c>
-      <c r="T42" s="3">
-        <v>5400</v>
       </c>
       <c r="U42" s="3">
         <v>5400</v>
@@ -4427,8 +4517,8 @@
       <c r="AD42" s="3">
         <v>5400</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>91</v>
+      <c r="AE42" s="3">
+        <v>5400</v>
       </c>
       <c r="AF42" s="3" t="s">
         <v>91</v>
@@ -4442,8 +4532,8 @@
       <c r="AI42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AJ42" s="3">
-        <v>0</v>
+      <c r="AJ42" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AK42" s="3">
         <v>0</v>
@@ -4463,252 +4553,261 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E43" s="3">
         <v>11000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>16400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>27900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>16000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>11300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>6300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>6800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>7400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>11100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>9600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>13800</v>
-      </c>
-      <c r="AO43" s="3">
-        <v>12400</v>
       </c>
       <c r="AP43" s="3">
         <v>12400</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>12400</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>13200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>11800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>800</v>
-      </c>
-      <c r="AF44" s="3">
-        <v>1900</v>
       </c>
       <c r="AG44" s="3">
         <v>1900</v>
       </c>
       <c r="AH44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AI44" s="3">
         <v>1600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2100</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
@@ -4716,19 +4815,19 @@
         <v>400</v>
       </c>
       <c r="E45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
         <v>200</v>
       </c>
       <c r="G45" s="3">
+        <v>200</v>
+      </c>
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
       </c>
       <c r="J45" s="3">
         <v>200</v>
@@ -4740,7 +4839,7 @@
         <v>200</v>
       </c>
       <c r="M45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
@@ -4749,25 +4848,25 @@
         <v>100</v>
       </c>
       <c r="P45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>200</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
       <c r="S45" s="3">
+        <v>200</v>
+      </c>
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
-      </c>
-      <c r="V45" s="3">
-        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>100</v>
@@ -4779,7 +4878,7 @@
         <v>100</v>
       </c>
       <c r="Z45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
@@ -4791,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="AD45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE45" s="3">
         <v>100</v>
@@ -4806,19 +4905,19 @@
         <v>100</v>
       </c>
       <c r="AI45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AJ45" s="3">
         <v>200</v>
       </c>
       <c r="AK45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AL45" s="3">
         <v>100</v>
       </c>
       <c r="AM45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AN45" s="3">
         <v>500</v>
@@ -4827,132 +4926,138 @@
         <v>500</v>
       </c>
       <c r="AP45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AQ45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E46" s="3">
         <v>47200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>47400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>45200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>48600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>45300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>47800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>46100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>51900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>47300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>50400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>47000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>48400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>53300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>45500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>47200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>54800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>74400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>106100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>79400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>61400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>25100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>25300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>20700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>19600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>21600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>27600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>21700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>19900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>21900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>21200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>28900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>23900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>28100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>25900</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>27900</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -4992,8 +5097,8 @@
       <c r="O47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -5073,91 +5178,94 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="E48" s="3">
         <v>1300</v>
       </c>
       <c r="F48" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="G48" s="3">
         <v>1500</v>
       </c>
       <c r="H48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I48" s="3">
         <v>1600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>200</v>
-      </c>
-      <c r="N48" s="3">
-        <v>300</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
       </c>
       <c r="P48" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q48" s="3">
         <v>400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>500</v>
-      </c>
-      <c r="R48" s="3">
-        <v>600</v>
       </c>
       <c r="S48" s="3">
         <v>600</v>
       </c>
       <c r="T48" s="3">
+        <v>600</v>
+      </c>
+      <c r="U48" s="3">
         <v>700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>1600</v>
       </c>
       <c r="AC48" s="3">
         <v>1600</v>
       </c>
       <c r="AD48" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="AE48" s="3">
         <v>100</v>
@@ -5175,7 +5283,7 @@
         <v>100</v>
       </c>
       <c r="AJ48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AK48" s="3">
         <v>200</v>
@@ -5187,7 +5295,7 @@
         <v>200</v>
       </c>
       <c r="AN48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AO48" s="3">
         <v>300</v>
@@ -5195,130 +5303,136 @@
       <c r="AP48" s="3">
         <v>300</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1300</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1100</v>
       </c>
       <c r="H49" s="3">
         <v>1100</v>
       </c>
       <c r="I49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J49" s="3">
         <v>1400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1900</v>
-      </c>
-      <c r="R49" s="3">
-        <v>1600</v>
       </c>
       <c r="S49" s="3">
         <v>1600</v>
       </c>
       <c r="T49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="U49" s="3">
         <v>1700</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1500</v>
       </c>
       <c r="V49" s="3">
         <v>1500</v>
       </c>
       <c r="W49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X49" s="3">
         <v>1600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1700</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>1400</v>
       </c>
       <c r="Z49" s="3">
         <v>1400</v>
       </c>
       <c r="AA49" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="AB49" s="3">
         <v>1500</v>
       </c>
       <c r="AC49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AD49" s="3">
         <v>1700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1400</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>1100</v>
       </c>
       <c r="AF49" s="3">
         <v>1100</v>
       </c>
       <c r="AG49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH49" s="3">
         <v>1200</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>1300</v>
       </c>
       <c r="AI49" s="3">
         <v>1300</v>
       </c>
       <c r="AJ49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AK49" s="3">
         <v>1400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1400</v>
-      </c>
-      <c r="AM49" s="3">
-        <v>1300</v>
       </c>
       <c r="AN49" s="3">
         <v>1300</v>
       </c>
       <c r="AO49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="AP49" s="3">
         <v>1400</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5561,8 +5678,11 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -5603,76 +5723,76 @@
         <v>100</v>
       </c>
       <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2100</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>2000</v>
       </c>
       <c r="AH52" s="3">
         <v>2000</v>
       </c>
       <c r="AI52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1800</v>
-      </c>
-      <c r="AM52" s="3">
-        <v>1900</v>
       </c>
       <c r="AN52" s="3">
         <v>1900</v>
@@ -5681,10 +5801,13 @@
         <v>1900</v>
       </c>
       <c r="AP52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AQ52" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E54" s="3">
         <v>53000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>53300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>51300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>49700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>54500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>50000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>52600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>50900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>56900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>52400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>54600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>51000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>52000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>57200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>49400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>50500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>57800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>78000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>109700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>83100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>65400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>26600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>21200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>24900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>30800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>25100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>25200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>24800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>32300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>27300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>31600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>29500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -6015,135 +6145,139 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E57" s="3">
         <v>10200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>27900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>63900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>44900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>42100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>13200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>7600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>7000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>5800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>12900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>7200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>11800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>10600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
@@ -6158,28 +6292,28 @@
         <v>400</v>
       </c>
       <c r="I58" s="3">
+        <v>400</v>
+      </c>
+      <c r="J58" s="3">
         <v>300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
-      </c>
-      <c r="N58" s="3">
-        <v>200</v>
       </c>
       <c r="O58" s="3">
         <v>200</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -6259,8 +6393,11 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
@@ -6286,79 +6423,79 @@
         <v>200</v>
       </c>
       <c r="K59" s="3">
+        <v>200</v>
+      </c>
+      <c r="L59" s="3">
         <v>2600</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2700</v>
       </c>
       <c r="M59" s="3">
         <v>2700</v>
       </c>
       <c r="N59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O59" s="3">
         <v>2600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1600</v>
-      </c>
-      <c r="U59" s="3">
-        <v>1400</v>
       </c>
       <c r="V59" s="3">
         <v>1400</v>
       </c>
       <c r="W59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X59" s="3">
         <v>3500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>200</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>300</v>
       </c>
       <c r="AF59" s="3">
         <v>300</v>
       </c>
       <c r="AG59" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AH59" s="3">
         <v>500</v>
       </c>
       <c r="AI59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AJ59" s="3">
         <v>300</v>
@@ -6370,141 +6507,147 @@
         <v>300</v>
       </c>
       <c r="AM59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN59" s="3">
         <v>1000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E60" s="3">
         <v>13900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>31300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>67300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>47500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>43000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>13200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>8200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>12600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>11000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
@@ -6512,19 +6655,19 @@
         <v>800</v>
       </c>
       <c r="E61" s="3">
+        <v>800</v>
+      </c>
+      <c r="F61" s="3">
         <v>900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1200</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1300</v>
       </c>
       <c r="J61" s="3">
         <v>1300</v>
@@ -6533,7 +6676,7 @@
         <v>1300</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -6625,8 +6768,11 @@
       <c r="AP61" s="3">
         <v>0</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
@@ -6666,50 +6812,50 @@
       <c r="O62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>100</v>
-      </c>
-      <c r="R62" s="3">
-        <v>200</v>
       </c>
       <c r="S62" s="3">
         <v>200</v>
       </c>
       <c r="T62" s="3">
+        <v>200</v>
+      </c>
+      <c r="U62" s="3">
         <v>300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>400</v>
-      </c>
-      <c r="V62" s="3">
-        <v>500</v>
       </c>
       <c r="W62" s="3">
         <v>500</v>
       </c>
       <c r="X62" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y62" s="3">
         <v>600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>91</v>
@@ -6726,8 +6872,8 @@
       <c r="AI62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AJ62" s="3">
-        <v>0</v>
+      <c r="AJ62" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AK62" s="3">
         <v>0</v>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>33300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>69100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>49700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>45000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>8200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>14200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>9200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>13600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>12000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7767,115 +7938,118 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E72" s="3">
         <v>25600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>24900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>28100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>29100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>30700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>30500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>30800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>32000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>32700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>33400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>34600</v>
-      </c>
-      <c r="V72" s="3">
-        <v>35700</v>
       </c>
       <c r="W72" s="3">
         <v>35700</v>
       </c>
       <c r="X72" s="3">
+        <v>35700</v>
+      </c>
+      <c r="Y72" s="3">
         <v>31800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>24900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>14500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>14700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15400</v>
-      </c>
-      <c r="AL72" s="3">
-        <v>15800</v>
       </c>
       <c r="AM72" s="3">
         <v>15800</v>
@@ -7884,13 +8058,16 @@
         <v>15800</v>
       </c>
       <c r="AO72" s="3">
+        <v>15800</v>
+      </c>
+      <c r="AP72" s="3">
         <v>15200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>35100</v>
+        <v>33500</v>
       </c>
       <c r="E76" s="3">
         <v>35100</v>
       </c>
       <c r="F76" s="3">
+        <v>35100</v>
+      </c>
+      <c r="G76" s="3">
         <v>34500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>35300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>36000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>35100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>36900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>38100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>38600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>38900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>40400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>40100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>39800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>41000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>42400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>43600</v>
-      </c>
-      <c r="V76" s="3">
-        <v>44700</v>
       </c>
       <c r="W76" s="3">
         <v>44700</v>
       </c>
       <c r="X76" s="3">
+        <v>44700</v>
+      </c>
+      <c r="Y76" s="3">
         <v>40700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>33400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>16300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>16100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>16900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>17000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17700</v>
-      </c>
-      <c r="AL76" s="3">
-        <v>18100</v>
       </c>
       <c r="AM76" s="3">
         <v>18100</v>
       </c>
       <c r="AN76" s="3">
+        <v>18100</v>
+      </c>
+      <c r="AO76" s="3">
         <v>18000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>17500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>3900</v>
-      </c>
-      <c r="X81" s="3">
-        <v>6900</v>
       </c>
       <c r="Y81" s="3">
         <v>6900</v>
       </c>
       <c r="Z81" s="3">
+        <v>6900</v>
+      </c>
+      <c r="AA81" s="3">
         <v>3700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-400</v>
       </c>
-      <c r="AL81" s="3">
-        <v>0</v>
-      </c>
       <c r="AM81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="3">
         <v>100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8792,8 +8990,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -8807,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -8834,7 +9033,7 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -8849,7 +9048,7 @@
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -8861,7 +9060,7 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>200</v>
@@ -8870,7 +9069,7 @@
         <v>200</v>
       </c>
       <c r="AB83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC83" s="3">
         <v>100</v>
@@ -8882,7 +9081,7 @@
         <v>100</v>
       </c>
       <c r="AF83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG83" s="3">
         <v>200</v>
@@ -8891,22 +9090,22 @@
         <v>200</v>
       </c>
       <c r="AI83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>100</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>200</v>
       </c>
       <c r="AK83" s="3">
         <v>200</v>
       </c>
       <c r="AL83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AM83" s="3">
         <v>100</v>
       </c>
       <c r="AN83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AO83" s="3">
         <v>200</v>
@@ -8914,8 +9113,11 @@
       <c r="AP83" s="3">
         <v>200</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5900</v>
-      </c>
-      <c r="H89" s="3">
-        <v>2700</v>
       </c>
       <c r="I89" s="3">
         <v>2700</v>
       </c>
       <c r="J89" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K89" s="3">
         <v>6200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-16600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>27900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>20100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4900</v>
       </c>
-      <c r="AH89" s="3">
-        <v>0</v>
-      </c>
       <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9690,8 +9910,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
@@ -9732,23 +9953,23 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -9768,23 +9989,23 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
@@ -9801,7 +10022,7 @@
         <v>0</v>
       </c>
       <c r="AM91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AN91" s="3">
         <v>-100</v>
@@ -9812,8 +10033,11 @@
       <c r="AP91" s="3">
         <v>-100</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10056,118 +10283,121 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W94" s="3">
         <v>-100</v>
       </c>
       <c r="X94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-500</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-100</v>
       </c>
       <c r="Z94" s="3">
         <v>-100</v>
       </c>
       <c r="AA94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-300</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
       <c r="AH94" s="3">
         <v>0</v>
       </c>
       <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ94" s="3">
-        <v>0</v>
-      </c>
       <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AM94" s="3">
-        <v>-100</v>
       </c>
       <c r="AN94" s="3">
         <v>-100</v>
@@ -10178,8 +10408,11 @@
       <c r="AP94" s="3">
         <v>-100</v>
       </c>
+      <c r="AQ94" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10222,16 +10455,17 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>500</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>91</v>
@@ -10263,8 +10497,8 @@
       <c r="O96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10710,22 +10953,25 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="F100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>91</v>
@@ -10733,12 +10979,12 @@
       <c r="I100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -10752,17 +10998,17 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -10779,13 +11025,13 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>6000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>500</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>91</v>
@@ -10793,14 +11039,14 @@
       <c r="AC100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="3" t="s">
+      <c r="AD100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AG100" s="3">
         <v>0</v>
@@ -10809,11 +11055,11 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>100</v>
       </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
       <c r="AK100" s="3">
         <v>0</v>
       </c>
@@ -10824,66 +11070,69 @@
         <v>0</v>
       </c>
       <c r="AN100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO100" s="3">
         <v>100</v>
       </c>
-      <c r="AO100" s="3">
-        <v>0</v>
-      </c>
       <c r="AP100" s="3">
         <v>0</v>
       </c>
+      <c r="AQ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-100</v>
       </c>
       <c r="T101" s="3">
         <v>-100</v>
@@ -10895,23 +11144,23 @@
         <v>-100</v>
       </c>
       <c r="W101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
@@ -10934,146 +11183,152 @@
         <v>0</v>
       </c>
       <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
         <v>100</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
       <c r="AL101" s="3">
         <v>0</v>
       </c>
       <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
         <v>100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-100</v>
-      </c>
-      <c r="AO101" s="3">
-        <v>100</v>
       </c>
       <c r="AP101" s="3">
         <v>100</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-8600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-16700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>27700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>15200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>20500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>3000</v>
       </c>
     </row>
